--- a/詳細設計図/メニュー画面_詳細設計図.xlsx
+++ b/詳細設計図/メニュー画面_詳細設計図.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-04\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-04\Documents\project\MyTaskSystem\詳細設計図\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42565959-927B-47D6-9D06-59277CF89B34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{830F4CCE-EB8F-4392-9C89-FFBE73930675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="10245" windowHeight="10920" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="93">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
   </si>
@@ -433,6 +433,22 @@
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
+  <si>
+    <t>task-add.jsp</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>POST</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>task-list.jsp</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>logout.jsp</t>
+    <phoneticPr fontId="8"/>
+  </si>
 </sst>
 </file>
 
@@ -519,7 +535,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="69">
+  <borders count="87">
     <border>
       <left/>
       <right/>
@@ -943,19 +959,6 @@
       <right style="medium">
         <color rgb="FF000000"/>
       </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
       <top/>
       <bottom/>
       <diagonal/>
@@ -969,17 +972,6 @@
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1331,11 +1323,239 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="117">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1366,37 +1586,28 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1405,18 +1616,24 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1426,28 +1643,22 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1474,113 +1685,113 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="64" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1603,56 +1814,59 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1660,32 +1874,116 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1965,85 +2263,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="44"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+      <c r="M2" s="41"/>
+      <c r="N2" s="41"/>
+      <c r="O2" s="41"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="42"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="42"/>
-      <c r="K3" s="42"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="42"/>
-      <c r="N3" s="42"/>
-      <c r="O3" s="42"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="39"/>
+      <c r="G3" s="39"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="39"/>
+      <c r="K3" s="39"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="39"/>
+      <c r="O3" s="39"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="42"/>
-      <c r="J4" s="42"/>
-      <c r="K4" s="42"/>
-      <c r="L4" s="42"/>
-      <c r="M4" s="42"/>
-      <c r="N4" s="42"/>
-      <c r="O4" s="42"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="39"/>
+      <c r="G4" s="39"/>
+      <c r="H4" s="39"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="39"/>
+      <c r="K4" s="39"/>
+      <c r="L4" s="39"/>
+      <c r="M4" s="39"/>
+      <c r="N4" s="39"/>
+      <c r="O4" s="39"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="42"/>
-      <c r="K5" s="42"/>
-      <c r="L5" s="42"/>
-      <c r="M5" s="42"/>
-      <c r="N5" s="42"/>
-      <c r="O5" s="42"/>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="39"/>
+      <c r="L5" s="39"/>
+      <c r="M5" s="39"/>
+      <c r="N5" s="39"/>
+      <c r="O5" s="39"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="42"/>
-      <c r="D6" s="42"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
-      <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="42"/>
-      <c r="J6" s="42"/>
-      <c r="K6" s="42"/>
-      <c r="L6" s="42"/>
-      <c r="M6" s="42"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="42"/>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="39"/>
+      <c r="L6" s="39"/>
+      <c r="M6" s="39"/>
+      <c r="N6" s="39"/>
+      <c r="O6" s="39"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2063,46 +2361,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="45" t="s">
+      <c r="E8" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="42"/>
-      <c r="K8" s="42"/>
-      <c r="L8" s="42"/>
-      <c r="M8" s="42"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="39"/>
+      <c r="K8" s="39"/>
+      <c r="L8" s="39"/>
+      <c r="M8" s="39"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="38" t="s">
+      <c r="G13" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="40"/>
-      <c r="I13" s="38" t="s">
+      <c r="H13" s="37"/>
+      <c r="I13" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="J13" s="39"/>
-      <c r="K13" s="40"/>
+      <c r="J13" s="36"/>
+      <c r="K13" s="37"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="38"/>
-      <c r="H14" s="40"/>
-      <c r="I14" s="38"/>
-      <c r="J14" s="39"/>
-      <c r="K14" s="40"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="37"/>
+      <c r="I14" s="35"/>
+      <c r="J14" s="36"/>
+      <c r="K14" s="37"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="38"/>
-      <c r="H15" s="40"/>
-      <c r="I15" s="38"/>
-      <c r="J15" s="39"/>
-      <c r="K15" s="40"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="37"/>
+      <c r="I15" s="35"/>
+      <c r="J15" s="36"/>
+      <c r="K15" s="37"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2111,13 +2409,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="41" t="s">
+      <c r="G17" s="38" t="s">
         <v>4</v>
       </c>
-      <c r="H17" s="42"/>
-      <c r="I17" s="42"/>
-      <c r="J17" s="42"/>
-      <c r="K17" s="42"/>
+      <c r="H17" s="39"/>
+      <c r="I17" s="39"/>
+      <c r="J17" s="39"/>
+      <c r="K17" s="39"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3131,19 +3429,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="62"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="77"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="44"/>
+      <c r="F1" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="77"/>
+      <c r="G1" s="44"/>
       <c r="H1" s="5" t="s">
         <v>8</v>
       </c>
@@ -3155,188 +3453,188 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="78" t="s">
+      <c r="A2" s="64"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="E2" s="79"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="81">
+      <c r="E2" s="46"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="49">
         <v>45705</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="74"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="75"/>
+      <c r="A3" s="64"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="62"/>
-      <c r="B4" s="64"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="75"/>
+      <c r="A4" s="64"/>
+      <c r="B4" s="65"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="53"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="65" t="s">
+      <c r="A5" s="66" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="49" t="s">
+      <c r="B5" s="67"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="74" t="s">
         <v>67</v>
       </c>
-      <c r="E5" s="50"/>
-      <c r="F5" s="50"/>
-      <c r="G5" s="50"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="50"/>
-      <c r="J5" s="51"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="75"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="67" t="s">
+      <c r="A6" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="52" t="s">
+      <c r="B6" s="36"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="76" t="s">
         <v>68</v>
       </c>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="53"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="57"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="67" t="s">
+      <c r="A7" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="40"/>
-      <c r="D7" s="52" t="s">
+      <c r="B7" s="36"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="76" t="s">
         <v>69</v>
       </c>
-      <c r="E7" s="39"/>
-      <c r="F7" s="39"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="53"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="57"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="67" t="s">
+      <c r="A8" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="39"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="52" t="s">
+      <c r="B8" s="36"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="76" t="s">
         <v>70</v>
       </c>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="53"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="36"/>
+      <c r="G8" s="36"/>
+      <c r="H8" s="36"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="57"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="68" t="s">
+      <c r="A9" s="69" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="71" t="s">
+      <c r="B9" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="40"/>
-      <c r="D9" s="54" t="s">
+      <c r="C9" s="37"/>
+      <c r="D9" s="56" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="55"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="55"/>
-      <c r="I9" s="55"/>
-      <c r="J9" s="56"/>
+      <c r="E9" s="77"/>
+      <c r="F9" s="77"/>
+      <c r="G9" s="77"/>
+      <c r="H9" s="77"/>
+      <c r="I9" s="77"/>
+      <c r="J9" s="78"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="69"/>
-      <c r="B10" s="71" t="s">
+      <c r="A10" s="70"/>
+      <c r="B10" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="54" t="s">
+      <c r="C10" s="37"/>
+      <c r="D10" s="56" t="s">
         <v>75</v>
       </c>
-      <c r="E10" s="39"/>
-      <c r="F10" s="39"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="39"/>
-      <c r="I10" s="39"/>
-      <c r="J10" s="53"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="36"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="57"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="70"/>
-      <c r="B11" s="71" t="s">
+      <c r="A11" s="71"/>
+      <c r="B11" s="54" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="54"/>
-      <c r="E11" s="39"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="39"/>
-      <c r="I11" s="39"/>
-      <c r="J11" s="53"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="56"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="36"/>
+      <c r="G11" s="36"/>
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
+      <c r="J11" s="57"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="67" t="s">
+      <c r="A12" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="54" t="s">
+      <c r="B12" s="36"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="56" t="s">
         <v>73</v>
       </c>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="53"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="36"/>
+      <c r="J12" s="57"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="57" t="s">
+      <c r="A13" s="58" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="47"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="46"/>
-      <c r="E13" s="47"/>
-      <c r="F13" s="47"/>
-      <c r="G13" s="47"/>
-      <c r="H13" s="47"/>
-      <c r="I13" s="47"/>
-      <c r="J13" s="48"/>
+      <c r="B13" s="59"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="59"/>
+      <c r="I13" s="59"/>
+      <c r="J13" s="73"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4327,17 +4625,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -4346,14 +4641,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4372,19 +4670,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="81" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="62"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="77"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="44"/>
+      <c r="F1" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="77"/>
+      <c r="G1" s="44"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -4396,40 +4694,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="74"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="75"/>
+      <c r="A3" s="64"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="85"/>
-      <c r="B4" s="86"/>
-      <c r="C4" s="87"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="87"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="87"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="83"/>
+      <c r="A4" s="82"/>
+      <c r="B4" s="83"/>
+      <c r="C4" s="84"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="84"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="79"/>
+      <c r="J4" s="80"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -5785,19 +6083,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="81" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="62"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="77"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="44"/>
+      <c r="F1" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="77"/>
+      <c r="G1" s="44"/>
       <c r="H1" s="4" t="s">
         <v>8</v>
       </c>
@@ -5809,40 +6107,40 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="78"/>
-      <c r="E2" s="79"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="74"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+      <c r="J2" s="52"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="75"/>
+      <c r="A3" s="64"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="53"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="85"/>
-      <c r="B4" s="86"/>
-      <c r="C4" s="87"/>
-      <c r="D4" s="88"/>
-      <c r="E4" s="87"/>
-      <c r="F4" s="88"/>
-      <c r="G4" s="87"/>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82"/>
-      <c r="J4" s="83"/>
+      <c r="A4" s="82"/>
+      <c r="B4" s="83"/>
+      <c r="C4" s="84"/>
+      <c r="D4" s="85"/>
+      <c r="E4" s="84"/>
+      <c r="F4" s="85"/>
+      <c r="G4" s="84"/>
+      <c r="H4" s="79"/>
+      <c r="I4" s="79"/>
+      <c r="J4" s="80"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7183,7 +7481,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J1002"/>
+  <dimension ref="A1:J997"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="5.140625" customWidth="1"/>
@@ -7192,386 +7490,437 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="84" t="s">
+      <c r="A1" s="114" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="61"/>
-      <c r="D1" s="76" t="s">
+      <c r="B1" s="115"/>
+      <c r="C1" s="116"/>
+      <c r="D1" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="77"/>
-      <c r="F1" s="76" t="s">
+      <c r="E1" s="68"/>
+      <c r="F1" s="117" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="77"/>
-      <c r="H1" s="4" t="s">
+      <c r="G1" s="68"/>
+      <c r="H1" s="118" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="119" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" s="120" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="63"/>
-      <c r="D2" s="78" t="s">
+      <c r="A2" s="121"/>
+      <c r="B2" s="112"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="45" t="s">
         <v>71</v>
       </c>
-      <c r="E2" s="79"/>
-      <c r="F2" s="78"/>
-      <c r="G2" s="79"/>
-      <c r="H2" s="81">
+      <c r="E2" s="46"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="46"/>
+      <c r="H2" s="49">
         <v>45707</v>
       </c>
-      <c r="I2" s="72" t="s">
+      <c r="I2" s="51" t="s">
         <v>72</v>
       </c>
-      <c r="J2" s="74"/>
+      <c r="J2" s="122"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="63"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="63"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="63"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="75"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="62"/>
-      <c r="B4" s="42"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="80"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="80"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
-      <c r="J4" s="75"/>
+      <c r="A3" s="121"/>
+      <c r="B3" s="112"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="50"/>
+      <c r="J3" s="123"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="121"/>
+      <c r="B4" s="112"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="50"/>
+      <c r="I4" s="50"/>
+      <c r="J4" s="123"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="94" t="s">
+      <c r="A5" s="124" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="95"/>
-      <c r="C5" s="77"/>
-      <c r="D5" s="99" t="s">
+      <c r="B5" s="88"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="91" t="s">
         <v>88</v>
       </c>
-      <c r="E5" s="95"/>
-      <c r="F5" s="95"/>
-      <c r="G5" s="95"/>
-      <c r="H5" s="95"/>
-      <c r="I5" s="95"/>
-      <c r="J5" s="100"/>
+      <c r="E5" s="88"/>
+      <c r="F5" s="88"/>
+      <c r="G5" s="88"/>
+      <c r="H5" s="88"/>
+      <c r="I5" s="88"/>
+      <c r="J5" s="125"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="98" t="s">
+      <c r="A6" s="126" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="93"/>
+      <c r="B6" s="36"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="36"/>
+      <c r="G6" s="36"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="57"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="101"/>
-      <c r="B7" s="102"/>
-      <c r="C7" s="102"/>
-      <c r="D7" s="102"/>
-      <c r="E7" s="102"/>
-      <c r="F7" s="102"/>
-      <c r="G7" s="102"/>
-      <c r="H7" s="102"/>
-      <c r="I7" s="102"/>
-      <c r="J7" s="103"/>
+      <c r="A7" s="127"/>
+      <c r="B7" s="94"/>
+      <c r="C7" s="94"/>
+      <c r="D7" s="94"/>
+      <c r="E7" s="94"/>
+      <c r="F7" s="94"/>
+      <c r="G7" s="94"/>
+      <c r="H7" s="94"/>
+      <c r="I7" s="94"/>
+      <c r="J7" s="128"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="62"/>
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
-      <c r="J8" s="104"/>
+      <c r="A8" s="121"/>
+      <c r="B8" s="112"/>
+      <c r="C8" s="112"/>
+      <c r="D8" s="112"/>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="112"/>
+      <c r="H8" s="112"/>
+      <c r="I8" s="112"/>
+      <c r="J8" s="129"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="62"/>
-      <c r="B9" s="42"/>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
-      <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="42"/>
-      <c r="J9" s="104"/>
+      <c r="A9" s="121"/>
+      <c r="B9" s="112"/>
+      <c r="C9" s="112"/>
+      <c r="D9" s="112"/>
+      <c r="E9" s="112"/>
+      <c r="F9" s="112"/>
+      <c r="G9" s="112"/>
+      <c r="H9" s="112"/>
+      <c r="I9" s="112"/>
+      <c r="J9" s="129"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="62"/>
-      <c r="B10" s="42"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="42"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
-      <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="104"/>
+      <c r="A10" s="121"/>
+      <c r="B10" s="112"/>
+      <c r="C10" s="112"/>
+      <c r="D10" s="112"/>
+      <c r="E10" s="112"/>
+      <c r="F10" s="112"/>
+      <c r="G10" s="112"/>
+      <c r="H10" s="112"/>
+      <c r="I10" s="112"/>
+      <c r="J10" s="129"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="62"/>
-      <c r="B11" s="42"/>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="104"/>
+      <c r="A11" s="121"/>
+      <c r="B11" s="112"/>
+      <c r="C11" s="112"/>
+      <c r="D11" s="112"/>
+      <c r="E11" s="112"/>
+      <c r="F11" s="112"/>
+      <c r="G11" s="112"/>
+      <c r="H11" s="112"/>
+      <c r="I11" s="112"/>
+      <c r="J11" s="129"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="62"/>
-      <c r="B12" s="42"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="104"/>
+      <c r="A12" s="121"/>
+      <c r="B12" s="112"/>
+      <c r="C12" s="112"/>
+      <c r="D12" s="112"/>
+      <c r="E12" s="112"/>
+      <c r="F12" s="112"/>
+      <c r="G12" s="112"/>
+      <c r="H12" s="112"/>
+      <c r="I12" s="112"/>
+      <c r="J12" s="129"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="62"/>
-      <c r="B13" s="42"/>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="42"/>
-      <c r="G13" s="42"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="42"/>
-      <c r="J13" s="104"/>
+      <c r="A13" s="130"/>
+      <c r="B13" s="113"/>
+      <c r="C13" s="113"/>
+      <c r="D13" s="113"/>
+      <c r="E13" s="113"/>
+      <c r="F13" s="113"/>
+      <c r="G13" s="113"/>
+      <c r="H13" s="113"/>
+      <c r="I13" s="113"/>
+      <c r="J13" s="131"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="98" t="s">
+      <c r="A14" s="132" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="39"/>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="39"/>
-      <c r="I14" s="39"/>
-      <c r="J14" s="93"/>
+      <c r="B14" s="111"/>
+      <c r="C14" s="111"/>
+      <c r="D14" s="111"/>
+      <c r="E14" s="111"/>
+      <c r="F14" s="111"/>
+      <c r="G14" s="111"/>
+      <c r="H14" s="111"/>
+      <c r="I14" s="111"/>
+      <c r="J14" s="133"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="98" t="s">
+      <c r="A15" s="126" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="39"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="52"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="40"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="37"/>
+      <c r="D15" s="76" t="s">
+        <v>89</v>
+      </c>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="37"/>
       <c r="I15" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="J15" s="16"/>
+      <c r="J15" s="134" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="98" t="s">
+      <c r="A16" s="126" t="s">
+        <v>29</v>
+      </c>
+      <c r="B16" s="36"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="H16" s="97" t="s">
+        <v>20</v>
+      </c>
+      <c r="I16" s="36"/>
+      <c r="J16" s="57"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A17" s="135" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" s="36"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="G17" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="H17" s="76" t="s">
+        <v>85</v>
+      </c>
+      <c r="I17" s="36"/>
+      <c r="J17" s="57"/>
+    </row>
+    <row r="18" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A18" s="126" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="36"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="36"/>
+      <c r="G18" s="36"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="36"/>
+      <c r="J18" s="57"/>
+    </row>
+    <row r="19" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A19" s="126" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="39"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="52"/>
-      <c r="E16" s="39"/>
-      <c r="F16" s="39"/>
-      <c r="G16" s="39"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="15" t="s">
+      <c r="B19" s="36"/>
+      <c r="C19" s="37"/>
+      <c r="D19" s="76" t="s">
+        <v>91</v>
+      </c>
+      <c r="E19" s="36"/>
+      <c r="F19" s="36"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="37"/>
+      <c r="I19" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="J16" s="16"/>
-    </row>
-    <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="98" t="s">
+      <c r="J19" s="134" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="126" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="36"/>
+      <c r="C20" s="37"/>
+      <c r="D20" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="F20" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G20" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="H20" s="97" t="s">
+        <v>20</v>
+      </c>
+      <c r="I20" s="36"/>
+      <c r="J20" s="57"/>
+    </row>
+    <row r="21" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A21" s="135" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" s="109"/>
+      <c r="C21" s="110"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16" t="s">
+        <v>81</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="G21" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="H21" s="76" t="s">
+        <v>86</v>
+      </c>
+      <c r="I21" s="77"/>
+      <c r="J21" s="78"/>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="126" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22" s="36"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="36"/>
+      <c r="J22" s="57"/>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A23" s="126" t="s">
         <v>27</v>
       </c>
-      <c r="B17" s="39"/>
-      <c r="C17" s="40"/>
-      <c r="D17" s="52"/>
-      <c r="E17" s="39"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="39"/>
-      <c r="H17" s="40"/>
-      <c r="I17" s="15" t="s">
+      <c r="B23" s="36"/>
+      <c r="C23" s="37"/>
+      <c r="D23" s="76" t="s">
+        <v>92</v>
+      </c>
+      <c r="E23" s="36"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="J17" s="16"/>
-    </row>
-    <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="98" t="s">
+      <c r="J23" s="134" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A24" s="126" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="39"/>
-      <c r="C18" s="40"/>
-      <c r="D18" s="15" t="s">
+      <c r="B24" s="36"/>
+      <c r="C24" s="37"/>
+      <c r="D24" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E24" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="F18" s="15" t="s">
+      <c r="F24" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="G18" s="15" t="s">
+      <c r="G24" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="H18" s="105" t="s">
+      <c r="H24" s="97" t="s">
         <v>20</v>
       </c>
-      <c r="I18" s="39"/>
-      <c r="J18" s="93"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="92" t="s">
-        <v>78</v>
-      </c>
-      <c r="B19" s="39"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17" t="s">
+      <c r="I24" s="36"/>
+      <c r="J24" s="57"/>
+    </row>
+    <row r="25" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A25" s="135" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" s="109"/>
+      <c r="C25" s="110"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16" t="s">
         <v>81</v>
       </c>
-      <c r="F19" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="G19" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="H19" s="52" t="s">
-        <v>85</v>
-      </c>
-      <c r="I19" s="39"/>
-      <c r="J19" s="93"/>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="92" t="s">
-        <v>79</v>
-      </c>
-      <c r="B20" s="39"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="F20" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="G20" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="H20" s="52" t="s">
-        <v>86</v>
-      </c>
-      <c r="I20" s="39"/>
-      <c r="J20" s="93"/>
-    </row>
-    <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="92" t="s">
-        <v>80</v>
-      </c>
-      <c r="B21" s="39"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="F21" s="18" t="s">
+      <c r="F25" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="G21" s="18" t="s">
+      <c r="G25" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="H21" s="52" t="s">
+      <c r="H25" s="76" t="s">
         <v>87</v>
       </c>
-      <c r="I21" s="39"/>
-      <c r="J21" s="93"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="92"/>
-      <c r="B22" s="39"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="17"/>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="52"/>
-      <c r="I22" s="39"/>
-      <c r="J22" s="93"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="92"/>
-      <c r="B23" s="39"/>
-      <c r="C23" s="40"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="52"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="93"/>
-    </row>
-    <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="92"/>
-      <c r="B24" s="39"/>
-      <c r="C24" s="40"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="52"/>
-      <c r="I24" s="39"/>
-      <c r="J24" s="93"/>
-    </row>
-    <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="96"/>
-      <c r="B25" s="90"/>
-      <c r="C25" s="97"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="20"/>
-      <c r="G25" s="20"/>
-      <c r="H25" s="89"/>
-      <c r="I25" s="90"/>
-      <c r="J25" s="91"/>
-    </row>
-    <row r="26" spans="1:10" ht="12.75" customHeight="1"/>
+      <c r="I25" s="77"/>
+      <c r="J25" s="78"/>
+    </row>
+    <row r="26" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
+      <c r="A26" s="136"/>
+      <c r="B26" s="137"/>
+      <c r="C26" s="138"/>
+      <c r="D26" s="139"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="140"/>
+      <c r="G26" s="140"/>
+      <c r="H26" s="72"/>
+      <c r="I26" s="141"/>
+      <c r="J26" s="142"/>
+    </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="28" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="29" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8543,18 +8892,32 @@
     <row r="995" ht="12.75" customHeight="1"/>
     <row r="996" ht="12.75" customHeight="1"/>
     <row r="997" ht="12.75" customHeight="1"/>
-    <row r="998" ht="12.75" customHeight="1"/>
-    <row r="999" ht="12.75" customHeight="1"/>
-    <row r="1000" ht="12.75" customHeight="1"/>
-    <row r="1001" ht="12.75" customHeight="1"/>
-    <row r="1002" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A16:C16"/>
-    <mergeCell ref="D16:H16"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="D15:H15"/>
@@ -8562,29 +8925,10 @@
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="F1:G1"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A18:C18"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
     <mergeCell ref="D2:E4"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H22:J22"/>
-    <mergeCell ref="H23:J23"/>
-    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8604,181 +8948,181 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="61" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="61"/>
-      <c r="G1" s="76" t="s">
+      <c r="B1" s="62"/>
+      <c r="C1" s="62"/>
+      <c r="D1" s="62"/>
+      <c r="E1" s="62"/>
+      <c r="F1" s="63"/>
+      <c r="G1" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="95"/>
-      <c r="I1" s="95"/>
-      <c r="J1" s="77"/>
-      <c r="K1" s="76" t="s">
+      <c r="H1" s="88"/>
+      <c r="I1" s="88"/>
+      <c r="J1" s="44"/>
+      <c r="K1" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="L1" s="95"/>
-      <c r="M1" s="95"/>
-      <c r="N1" s="77"/>
-      <c r="O1" s="76" t="s">
+      <c r="L1" s="88"/>
+      <c r="M1" s="88"/>
+      <c r="N1" s="44"/>
+      <c r="O1" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="77"/>
-      <c r="Q1" s="76" t="s">
+      <c r="P1" s="44"/>
+      <c r="Q1" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="R1" s="77"/>
-      <c r="S1" s="76" t="s">
+      <c r="R1" s="44"/>
+      <c r="S1" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="T1" s="100"/>
+      <c r="T1" s="92"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="62"/>
-      <c r="B2" s="42"/>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="63"/>
-      <c r="G2" s="78"/>
-      <c r="H2" s="102"/>
-      <c r="I2" s="102"/>
-      <c r="J2" s="79"/>
-      <c r="K2" s="78"/>
-      <c r="L2" s="102"/>
-      <c r="M2" s="102"/>
-      <c r="N2" s="79"/>
-      <c r="O2" s="78"/>
-      <c r="P2" s="79"/>
-      <c r="Q2" s="78"/>
-      <c r="R2" s="79"/>
-      <c r="S2" s="78"/>
-      <c r="T2" s="103"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="45"/>
+      <c r="H2" s="94"/>
+      <c r="I2" s="94"/>
+      <c r="J2" s="46"/>
+      <c r="K2" s="45"/>
+      <c r="L2" s="94"/>
+      <c r="M2" s="94"/>
+      <c r="N2" s="46"/>
+      <c r="O2" s="45"/>
+      <c r="P2" s="46"/>
+      <c r="Q2" s="45"/>
+      <c r="R2" s="46"/>
+      <c r="S2" s="45"/>
+      <c r="T2" s="95"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="62"/>
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="63"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="42"/>
-      <c r="I3" s="42"/>
-      <c r="J3" s="63"/>
-      <c r="K3" s="80"/>
-      <c r="L3" s="42"/>
-      <c r="M3" s="42"/>
-      <c r="N3" s="63"/>
-      <c r="O3" s="80"/>
-      <c r="P3" s="63"/>
-      <c r="Q3" s="80"/>
-      <c r="R3" s="63"/>
-      <c r="S3" s="80"/>
-      <c r="T3" s="104"/>
+      <c r="A3" s="64"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="39"/>
+      <c r="D3" s="39"/>
+      <c r="E3" s="39"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="39"/>
+      <c r="I3" s="39"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="39"/>
+      <c r="M3" s="39"/>
+      <c r="N3" s="48"/>
+      <c r="O3" s="47"/>
+      <c r="P3" s="48"/>
+      <c r="Q3" s="47"/>
+      <c r="R3" s="48"/>
+      <c r="S3" s="47"/>
+      <c r="T3" s="96"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="85"/>
-      <c r="B4" s="86"/>
-      <c r="C4" s="86"/>
-      <c r="D4" s="86"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="87"/>
-      <c r="G4" s="88"/>
-      <c r="H4" s="86"/>
-      <c r="I4" s="86"/>
-      <c r="J4" s="87"/>
-      <c r="K4" s="88"/>
-      <c r="L4" s="86"/>
-      <c r="M4" s="86"/>
-      <c r="N4" s="87"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="87"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="87"/>
-      <c r="S4" s="88"/>
-      <c r="T4" s="115"/>
+      <c r="A4" s="82"/>
+      <c r="B4" s="83"/>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="84"/>
+      <c r="G4" s="85"/>
+      <c r="H4" s="83"/>
+      <c r="I4" s="83"/>
+      <c r="J4" s="84"/>
+      <c r="K4" s="85"/>
+      <c r="L4" s="83"/>
+      <c r="M4" s="83"/>
+      <c r="N4" s="84"/>
+      <c r="O4" s="85"/>
+      <c r="P4" s="84"/>
+      <c r="Q4" s="85"/>
+      <c r="R4" s="84"/>
+      <c r="S4" s="85"/>
+      <c r="T4" s="102"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="94" t="s">
+      <c r="A5" s="87" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="95"/>
-      <c r="C5" s="95"/>
-      <c r="D5" s="95"/>
-      <c r="E5" s="95"/>
-      <c r="F5" s="77"/>
-      <c r="G5" s="112" t="s">
+      <c r="B5" s="88"/>
+      <c r="C5" s="88"/>
+      <c r="D5" s="88"/>
+      <c r="E5" s="88"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="103" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="95"/>
-      <c r="I5" s="95"/>
-      <c r="J5" s="95"/>
-      <c r="K5" s="95"/>
-      <c r="L5" s="95"/>
-      <c r="M5" s="95"/>
-      <c r="N5" s="95"/>
-      <c r="O5" s="95"/>
-      <c r="P5" s="95"/>
-      <c r="Q5" s="95"/>
-      <c r="R5" s="95"/>
-      <c r="S5" s="95"/>
-      <c r="T5" s="100"/>
+      <c r="H5" s="88"/>
+      <c r="I5" s="88"/>
+      <c r="J5" s="88"/>
+      <c r="K5" s="88"/>
+      <c r="L5" s="88"/>
+      <c r="M5" s="88"/>
+      <c r="N5" s="88"/>
+      <c r="O5" s="88"/>
+      <c r="P5" s="88"/>
+      <c r="Q5" s="88"/>
+      <c r="R5" s="88"/>
+      <c r="S5" s="88"/>
+      <c r="T5" s="92"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="98" t="s">
+      <c r="A6" s="86" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="39"/>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="52" t="s">
+      <c r="B6" s="36"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="76" t="s">
         <v>21</v>
       </c>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="39"/>
-      <c r="M6" s="39"/>
-      <c r="N6" s="39"/>
-      <c r="O6" s="39"/>
-      <c r="P6" s="39"/>
-      <c r="Q6" s="39"/>
-      <c r="R6" s="39"/>
-      <c r="S6" s="39"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="36"/>
+      <c r="K6" s="36"/>
+      <c r="L6" s="36"/>
+      <c r="M6" s="36"/>
+      <c r="N6" s="36"/>
+      <c r="O6" s="36"/>
+      <c r="P6" s="36"/>
+      <c r="Q6" s="36"/>
+      <c r="R6" s="36"/>
+      <c r="S6" s="36"/>
       <c r="T6" s="93"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="98" t="s">
+      <c r="A7" s="86" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="39"/>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="52" t="s">
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="76" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="39"/>
-      <c r="K7" s="39"/>
-      <c r="L7" s="39"/>
-      <c r="M7" s="39"/>
-      <c r="N7" s="39"/>
-      <c r="O7" s="39"/>
-      <c r="P7" s="39"/>
-      <c r="Q7" s="39"/>
-      <c r="R7" s="39"/>
-      <c r="S7" s="39"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="36"/>
+      <c r="K7" s="36"/>
+      <c r="L7" s="36"/>
+      <c r="M7" s="36"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="36"/>
+      <c r="S7" s="36"/>
       <c r="T7" s="93"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
@@ -8804,156 +9148,156 @@
       <c r="T8" s="10"/>
     </row>
     <row r="9" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A9" s="21"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="23" t="s">
+      <c r="A9" s="18"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="24"/>
-      <c r="E9" s="24" t="s">
+      <c r="D9" s="21"/>
+      <c r="E9" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="F9" s="24"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="24"/>
-      <c r="I9" s="24"/>
-      <c r="J9" s="24"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="22"/>
-      <c r="N9" s="22"/>
-      <c r="O9" s="22"/>
-      <c r="P9" s="22"/>
-      <c r="Q9" s="22"/>
-      <c r="R9" s="22"/>
-      <c r="S9" s="22"/>
-      <c r="T9" s="26"/>
-      <c r="U9" s="22"/>
-      <c r="V9" s="22"/>
-      <c r="W9" s="22"/>
-      <c r="X9" s="22"/>
-      <c r="Y9" s="22"/>
-      <c r="Z9" s="22"/>
+      <c r="F9" s="21"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="22"/>
+      <c r="L9" s="19"/>
+      <c r="M9" s="19"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="19"/>
+      <c r="P9" s="19"/>
+      <c r="Q9" s="19"/>
+      <c r="R9" s="19"/>
+      <c r="S9" s="19"/>
+      <c r="T9" s="23"/>
+      <c r="U9" s="19"/>
+      <c r="V9" s="19"/>
+      <c r="W9" s="19"/>
+      <c r="X9" s="19"/>
+      <c r="Y9" s="19"/>
+      <c r="Z9" s="19"/>
     </row>
     <row r="10" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A10" s="21"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="22" t="s">
+      <c r="A10" s="18"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="22"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="28"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="22"/>
-      <c r="N10" s="22"/>
-      <c r="O10" s="22"/>
-      <c r="P10" s="22"/>
-      <c r="Q10" s="22"/>
-      <c r="R10" s="22"/>
-      <c r="S10" s="22"/>
-      <c r="T10" s="26"/>
-      <c r="U10" s="22"/>
-      <c r="V10" s="22"/>
-      <c r="W10" s="22"/>
-      <c r="X10" s="22"/>
-      <c r="Y10" s="22"/>
-      <c r="Z10" s="22"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="19"/>
+      <c r="M10" s="19"/>
+      <c r="N10" s="19"/>
+      <c r="O10" s="19"/>
+      <c r="P10" s="19"/>
+      <c r="Q10" s="19"/>
+      <c r="R10" s="19"/>
+      <c r="S10" s="19"/>
+      <c r="T10" s="23"/>
+      <c r="U10" s="19"/>
+      <c r="V10" s="19"/>
+      <c r="W10" s="19"/>
+      <c r="X10" s="19"/>
+      <c r="Y10" s="19"/>
+      <c r="Z10" s="19"/>
     </row>
     <row r="11" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A11" s="21"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="22" t="s">
+      <c r="A11" s="18"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="22"/>
-      <c r="G11" s="28"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="28"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="22"/>
-      <c r="O11" s="22"/>
-      <c r="P11" s="22"/>
-      <c r="Q11" s="22"/>
-      <c r="R11" s="22"/>
-      <c r="S11" s="22"/>
-      <c r="T11" s="26"/>
-      <c r="U11" s="22"/>
-      <c r="V11" s="22"/>
-      <c r="W11" s="22"/>
-      <c r="X11" s="22"/>
-      <c r="Y11" s="22"/>
-      <c r="Z11" s="22"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
+      <c r="O11" s="19"/>
+      <c r="P11" s="19"/>
+      <c r="Q11" s="19"/>
+      <c r="R11" s="19"/>
+      <c r="S11" s="19"/>
+      <c r="T11" s="23"/>
+      <c r="U11" s="19"/>
+      <c r="V11" s="19"/>
+      <c r="W11" s="19"/>
+      <c r="X11" s="19"/>
+      <c r="Y11" s="19"/>
+      <c r="Z11" s="19"/>
     </row>
     <row r="12" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A12" s="21"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="22" t="s">
+      <c r="A12" s="18"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="24"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="F12" s="22"/>
-      <c r="G12" s="28"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="28"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="22"/>
-      <c r="O12" s="22"/>
-      <c r="P12" s="22"/>
-      <c r="Q12" s="22"/>
-      <c r="R12" s="22"/>
-      <c r="S12" s="22"/>
-      <c r="T12" s="26"/>
-      <c r="U12" s="22"/>
-      <c r="V12" s="22"/>
-      <c r="W12" s="22"/>
-      <c r="X12" s="22"/>
-      <c r="Y12" s="22"/>
-      <c r="Z12" s="22"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="19"/>
+      <c r="M12" s="19"/>
+      <c r="N12" s="19"/>
+      <c r="O12" s="19"/>
+      <c r="P12" s="19"/>
+      <c r="Q12" s="19"/>
+      <c r="R12" s="19"/>
+      <c r="S12" s="19"/>
+      <c r="T12" s="23"/>
+      <c r="U12" s="19"/>
+      <c r="V12" s="19"/>
+      <c r="W12" s="19"/>
+      <c r="X12" s="19"/>
+      <c r="Y12" s="19"/>
+      <c r="Z12" s="19"/>
     </row>
     <row r="13" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A13" s="21"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="30"/>
-      <c r="E13" s="30" t="s">
+      <c r="A13" s="18"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="F13" s="30"/>
-      <c r="G13" s="31"/>
-      <c r="H13" s="30"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="30"/>
-      <c r="K13" s="31"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="22"/>
-      <c r="N13" s="22"/>
-      <c r="O13" s="22"/>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="22"/>
-      <c r="R13" s="22"/>
-      <c r="S13" s="22"/>
-      <c r="T13" s="26"/>
-      <c r="U13" s="22"/>
-      <c r="V13" s="22"/>
-      <c r="W13" s="22"/>
-      <c r="X13" s="22"/>
-      <c r="Y13" s="22"/>
-      <c r="Z13" s="22"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="19"/>
+      <c r="N13" s="19"/>
+      <c r="O13" s="19"/>
+      <c r="P13" s="19"/>
+      <c r="Q13" s="19"/>
+      <c r="R13" s="19"/>
+      <c r="S13" s="19"/>
+      <c r="T13" s="23"/>
+      <c r="U13" s="19"/>
+      <c r="V13" s="19"/>
+      <c r="W13" s="19"/>
+      <c r="X13" s="19"/>
+      <c r="Y13" s="19"/>
+      <c r="Z13" s="19"/>
     </row>
     <row r="14" spans="1:26" ht="8.25" customHeight="1">
       <c r="A14" s="8"/>
@@ -8978,526 +9322,526 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="98" t="s">
+      <c r="A15" s="86" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="40"/>
-      <c r="C15" s="114" t="s">
+      <c r="B15" s="37"/>
+      <c r="C15" s="106" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="40"/>
-      <c r="E15" s="105" t="s">
+      <c r="D15" s="37"/>
+      <c r="E15" s="97" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="40"/>
-      <c r="G15" s="105" t="s">
+      <c r="F15" s="37"/>
+      <c r="G15" s="97" t="s">
         <v>48</v>
       </c>
-      <c r="H15" s="39"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="105" t="s">
+      <c r="H15" s="36"/>
+      <c r="I15" s="37"/>
+      <c r="J15" s="97" t="s">
         <v>49</v>
       </c>
-      <c r="K15" s="40"/>
-      <c r="L15" s="105" t="s">
+      <c r="K15" s="37"/>
+      <c r="L15" s="97" t="s">
         <v>50</v>
       </c>
-      <c r="M15" s="39"/>
-      <c r="N15" s="40"/>
-      <c r="O15" s="105" t="s">
+      <c r="M15" s="36"/>
+      <c r="N15" s="37"/>
+      <c r="O15" s="97" t="s">
         <v>51</v>
       </c>
-      <c r="P15" s="39"/>
-      <c r="Q15" s="40"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="37"/>
       <c r="R15" s="15" t="s">
         <v>52</v>
       </c>
       <c r="S15" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="T15" s="32" t="s">
+      <c r="T15" s="29" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="106">
+      <c r="A16" s="104">
         <v>1</v>
       </c>
-      <c r="B16" s="40"/>
-      <c r="C16" s="107" t="s">
+      <c r="B16" s="37"/>
+      <c r="C16" s="105" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="40"/>
-      <c r="E16" s="107" t="s">
+      <c r="D16" s="37"/>
+      <c r="E16" s="105" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="113" t="s">
+      <c r="F16" s="37"/>
+      <c r="G16" s="98" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="39"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="113" t="s">
+      <c r="H16" s="36"/>
+      <c r="I16" s="37"/>
+      <c r="J16" s="98" t="s">
         <v>58</v>
       </c>
-      <c r="K16" s="40"/>
-      <c r="L16" s="110" t="s">
+      <c r="K16" s="37"/>
+      <c r="L16" s="100" t="s">
         <v>59</v>
       </c>
-      <c r="M16" s="39"/>
-      <c r="N16" s="40"/>
-      <c r="O16" s="110" t="s">
+      <c r="M16" s="36"/>
+      <c r="N16" s="37"/>
+      <c r="O16" s="100" t="s">
         <v>60</v>
       </c>
-      <c r="P16" s="39"/>
-      <c r="Q16" s="40"/>
-      <c r="R16" s="33"/>
-      <c r="S16" s="33"/>
-      <c r="T16" s="34"/>
-      <c r="U16" s="35"/>
-      <c r="V16" s="35"/>
-      <c r="W16" s="35"/>
-      <c r="X16" s="35"/>
-      <c r="Y16" s="35"/>
-      <c r="Z16" s="35"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="37"/>
+      <c r="R16" s="30"/>
+      <c r="S16" s="30"/>
+      <c r="T16" s="31"/>
+      <c r="U16" s="32"/>
+      <c r="V16" s="32"/>
+      <c r="W16" s="32"/>
+      <c r="X16" s="32"/>
+      <c r="Y16" s="32"/>
+      <c r="Z16" s="32"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="106">
+      <c r="A17" s="104">
         <v>2</v>
       </c>
-      <c r="B17" s="40"/>
-      <c r="C17" s="107" t="s">
+      <c r="B17" s="37"/>
+      <c r="C17" s="105" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="40"/>
-      <c r="E17" s="107" t="s">
+      <c r="D17" s="37"/>
+      <c r="E17" s="105" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="40"/>
-      <c r="G17" s="113" t="s">
+      <c r="F17" s="37"/>
+      <c r="G17" s="98" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="39"/>
-      <c r="I17" s="40"/>
-      <c r="J17" s="113" t="s">
+      <c r="H17" s="36"/>
+      <c r="I17" s="37"/>
+      <c r="J17" s="98" t="s">
         <v>64</v>
       </c>
-      <c r="K17" s="40"/>
-      <c r="L17" s="110" t="s">
+      <c r="K17" s="37"/>
+      <c r="L17" s="100" t="s">
         <v>65</v>
       </c>
-      <c r="M17" s="39"/>
-      <c r="N17" s="40"/>
-      <c r="O17" s="110" t="s">
+      <c r="M17" s="36"/>
+      <c r="N17" s="37"/>
+      <c r="O17" s="100" t="s">
         <v>66</v>
       </c>
-      <c r="P17" s="39"/>
-      <c r="Q17" s="40"/>
-      <c r="R17" s="33"/>
-      <c r="S17" s="33"/>
-      <c r="T17" s="34"/>
-      <c r="U17" s="35"/>
-      <c r="V17" s="35"/>
-      <c r="W17" s="35"/>
-      <c r="X17" s="35"/>
-      <c r="Y17" s="35"/>
-      <c r="Z17" s="35"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="37"/>
+      <c r="R17" s="30"/>
+      <c r="S17" s="30"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="32"/>
+      <c r="V17" s="32"/>
+      <c r="W17" s="32"/>
+      <c r="X17" s="32"/>
+      <c r="Y17" s="32"/>
+      <c r="Z17" s="32"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="106"/>
-      <c r="B18" s="40"/>
-      <c r="C18" s="107"/>
-      <c r="D18" s="40"/>
-      <c r="E18" s="107"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="113" t="s">
+      <c r="A18" s="104"/>
+      <c r="B18" s="37"/>
+      <c r="C18" s="105"/>
+      <c r="D18" s="37"/>
+      <c r="E18" s="105"/>
+      <c r="F18" s="37"/>
+      <c r="G18" s="98" t="s">
         <v>76</v>
       </c>
-      <c r="H18" s="39"/>
-      <c r="I18" s="40"/>
-      <c r="J18" s="113"/>
-      <c r="K18" s="40"/>
-      <c r="L18" s="110"/>
-      <c r="M18" s="39"/>
-      <c r="N18" s="40"/>
-      <c r="O18" s="110"/>
-      <c r="P18" s="39"/>
-      <c r="Q18" s="40"/>
-      <c r="R18" s="33"/>
-      <c r="S18" s="33"/>
-      <c r="T18" s="34"/>
-      <c r="U18" s="35"/>
-      <c r="V18" s="35"/>
-      <c r="W18" s="35"/>
-      <c r="X18" s="35"/>
-      <c r="Y18" s="35"/>
-      <c r="Z18" s="35"/>
+      <c r="H18" s="36"/>
+      <c r="I18" s="37"/>
+      <c r="J18" s="98"/>
+      <c r="K18" s="37"/>
+      <c r="L18" s="100"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="37"/>
+      <c r="O18" s="100"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="37"/>
+      <c r="R18" s="30"/>
+      <c r="S18" s="30"/>
+      <c r="T18" s="31"/>
+      <c r="U18" s="32"/>
+      <c r="V18" s="32"/>
+      <c r="W18" s="32"/>
+      <c r="X18" s="32"/>
+      <c r="Y18" s="32"/>
+      <c r="Z18" s="32"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="106"/>
-      <c r="B19" s="40"/>
-      <c r="C19" s="107"/>
-      <c r="D19" s="40"/>
-      <c r="E19" s="107"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="113" t="s">
+      <c r="A19" s="104"/>
+      <c r="B19" s="37"/>
+      <c r="C19" s="105"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="105"/>
+      <c r="F19" s="37"/>
+      <c r="G19" s="98" t="s">
         <v>77</v>
       </c>
-      <c r="H19" s="39"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="113"/>
-      <c r="K19" s="40"/>
-      <c r="L19" s="110"/>
-      <c r="M19" s="39"/>
-      <c r="N19" s="40"/>
-      <c r="O19" s="110"/>
-      <c r="P19" s="39"/>
-      <c r="Q19" s="40"/>
-      <c r="R19" s="33"/>
-      <c r="S19" s="33"/>
-      <c r="T19" s="34"/>
-      <c r="U19" s="35"/>
-      <c r="V19" s="35"/>
-      <c r="W19" s="35"/>
-      <c r="X19" s="35"/>
-      <c r="Y19" s="35"/>
-      <c r="Z19" s="35"/>
+      <c r="H19" s="36"/>
+      <c r="I19" s="37"/>
+      <c r="J19" s="98"/>
+      <c r="K19" s="37"/>
+      <c r="L19" s="100"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="37"/>
+      <c r="O19" s="100"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="37"/>
+      <c r="R19" s="30"/>
+      <c r="S19" s="30"/>
+      <c r="T19" s="31"/>
+      <c r="U19" s="32"/>
+      <c r="V19" s="32"/>
+      <c r="W19" s="32"/>
+      <c r="X19" s="32"/>
+      <c r="Y19" s="32"/>
+      <c r="Z19" s="32"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="106"/>
-      <c r="B20" s="40"/>
-      <c r="C20" s="107"/>
-      <c r="D20" s="40"/>
-      <c r="E20" s="107"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="113"/>
-      <c r="H20" s="39"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="113"/>
-      <c r="K20" s="40"/>
-      <c r="L20" s="110"/>
-      <c r="M20" s="39"/>
-      <c r="N20" s="40"/>
-      <c r="O20" s="110"/>
-      <c r="P20" s="39"/>
-      <c r="Q20" s="40"/>
-      <c r="R20" s="33"/>
-      <c r="S20" s="33"/>
-      <c r="T20" s="34"/>
-      <c r="U20" s="35"/>
-      <c r="V20" s="35"/>
-      <c r="W20" s="35"/>
-      <c r="X20" s="35"/>
-      <c r="Y20" s="35"/>
-      <c r="Z20" s="35"/>
+      <c r="A20" s="104"/>
+      <c r="B20" s="37"/>
+      <c r="C20" s="105"/>
+      <c r="D20" s="37"/>
+      <c r="E20" s="105"/>
+      <c r="F20" s="37"/>
+      <c r="G20" s="98"/>
+      <c r="H20" s="36"/>
+      <c r="I20" s="37"/>
+      <c r="J20" s="98"/>
+      <c r="K20" s="37"/>
+      <c r="L20" s="100"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="37"/>
+      <c r="O20" s="100"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="37"/>
+      <c r="R20" s="30"/>
+      <c r="S20" s="30"/>
+      <c r="T20" s="31"/>
+      <c r="U20" s="32"/>
+      <c r="V20" s="32"/>
+      <c r="W20" s="32"/>
+      <c r="X20" s="32"/>
+      <c r="Y20" s="32"/>
+      <c r="Z20" s="32"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="106"/>
-      <c r="B21" s="40"/>
-      <c r="C21" s="107"/>
-      <c r="D21" s="40"/>
-      <c r="E21" s="107"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="113"/>
-      <c r="H21" s="39"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="113"/>
-      <c r="K21" s="40"/>
-      <c r="L21" s="110"/>
-      <c r="M21" s="39"/>
-      <c r="N21" s="40"/>
-      <c r="O21" s="110"/>
-      <c r="P21" s="39"/>
-      <c r="Q21" s="40"/>
-      <c r="R21" s="33"/>
-      <c r="S21" s="33"/>
-      <c r="T21" s="34"/>
-      <c r="U21" s="35"/>
-      <c r="V21" s="35"/>
-      <c r="W21" s="35"/>
-      <c r="X21" s="35"/>
-      <c r="Y21" s="35"/>
-      <c r="Z21" s="35"/>
+      <c r="A21" s="104"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="105"/>
+      <c r="D21" s="37"/>
+      <c r="E21" s="105"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="98"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="37"/>
+      <c r="J21" s="98"/>
+      <c r="K21" s="37"/>
+      <c r="L21" s="100"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="37"/>
+      <c r="O21" s="100"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="37"/>
+      <c r="R21" s="30"/>
+      <c r="S21" s="30"/>
+      <c r="T21" s="31"/>
+      <c r="U21" s="32"/>
+      <c r="V21" s="32"/>
+      <c r="W21" s="32"/>
+      <c r="X21" s="32"/>
+      <c r="Y21" s="32"/>
+      <c r="Z21" s="32"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="106"/>
-      <c r="B22" s="40"/>
-      <c r="C22" s="107"/>
-      <c r="D22" s="40"/>
-      <c r="E22" s="107"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="113"/>
-      <c r="H22" s="39"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="113"/>
-      <c r="K22" s="40"/>
-      <c r="L22" s="110"/>
-      <c r="M22" s="39"/>
-      <c r="N22" s="40"/>
-      <c r="O22" s="110"/>
-      <c r="P22" s="39"/>
-      <c r="Q22" s="40"/>
-      <c r="R22" s="33"/>
-      <c r="S22" s="33"/>
-      <c r="T22" s="34"/>
-      <c r="U22" s="35"/>
-      <c r="V22" s="35"/>
-      <c r="W22" s="35"/>
-      <c r="X22" s="35"/>
-      <c r="Y22" s="35"/>
-      <c r="Z22" s="35"/>
+      <c r="A22" s="104"/>
+      <c r="B22" s="37"/>
+      <c r="C22" s="105"/>
+      <c r="D22" s="37"/>
+      <c r="E22" s="105"/>
+      <c r="F22" s="37"/>
+      <c r="G22" s="98"/>
+      <c r="H22" s="36"/>
+      <c r="I22" s="37"/>
+      <c r="J22" s="98"/>
+      <c r="K22" s="37"/>
+      <c r="L22" s="100"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="37"/>
+      <c r="O22" s="100"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="37"/>
+      <c r="R22" s="30"/>
+      <c r="S22" s="30"/>
+      <c r="T22" s="31"/>
+      <c r="U22" s="32"/>
+      <c r="V22" s="32"/>
+      <c r="W22" s="32"/>
+      <c r="X22" s="32"/>
+      <c r="Y22" s="32"/>
+      <c r="Z22" s="32"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="106"/>
-      <c r="B23" s="40"/>
-      <c r="C23" s="107"/>
-      <c r="D23" s="40"/>
-      <c r="E23" s="107"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="113"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="113"/>
-      <c r="K23" s="40"/>
-      <c r="L23" s="110"/>
-      <c r="M23" s="39"/>
-      <c r="N23" s="40"/>
-      <c r="O23" s="110"/>
-      <c r="P23" s="39"/>
-      <c r="Q23" s="40"/>
-      <c r="R23" s="33"/>
-      <c r="S23" s="33"/>
-      <c r="T23" s="34"/>
-      <c r="U23" s="35"/>
-      <c r="V23" s="35"/>
-      <c r="W23" s="35"/>
-      <c r="X23" s="35"/>
-      <c r="Y23" s="35"/>
-      <c r="Z23" s="35"/>
+      <c r="A23" s="104"/>
+      <c r="B23" s="37"/>
+      <c r="C23" s="105"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="105"/>
+      <c r="F23" s="37"/>
+      <c r="G23" s="98"/>
+      <c r="H23" s="36"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="98"/>
+      <c r="K23" s="37"/>
+      <c r="L23" s="100"/>
+      <c r="M23" s="36"/>
+      <c r="N23" s="37"/>
+      <c r="O23" s="100"/>
+      <c r="P23" s="36"/>
+      <c r="Q23" s="37"/>
+      <c r="R23" s="30"/>
+      <c r="S23" s="30"/>
+      <c r="T23" s="31"/>
+      <c r="U23" s="32"/>
+      <c r="V23" s="32"/>
+      <c r="W23" s="32"/>
+      <c r="X23" s="32"/>
+      <c r="Y23" s="32"/>
+      <c r="Z23" s="32"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="106"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="107"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="107"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="113"/>
-      <c r="H24" s="39"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="113"/>
-      <c r="K24" s="40"/>
-      <c r="L24" s="110"/>
-      <c r="M24" s="39"/>
-      <c r="N24" s="40"/>
-      <c r="O24" s="110"/>
-      <c r="P24" s="39"/>
-      <c r="Q24" s="40"/>
-      <c r="R24" s="33"/>
-      <c r="S24" s="33"/>
-      <c r="T24" s="34"/>
-      <c r="U24" s="35"/>
-      <c r="V24" s="35"/>
-      <c r="W24" s="35"/>
-      <c r="X24" s="35"/>
-      <c r="Y24" s="35"/>
-      <c r="Z24" s="35"/>
+      <c r="A24" s="104"/>
+      <c r="B24" s="37"/>
+      <c r="C24" s="105"/>
+      <c r="D24" s="37"/>
+      <c r="E24" s="105"/>
+      <c r="F24" s="37"/>
+      <c r="G24" s="98"/>
+      <c r="H24" s="36"/>
+      <c r="I24" s="37"/>
+      <c r="J24" s="98"/>
+      <c r="K24" s="37"/>
+      <c r="L24" s="100"/>
+      <c r="M24" s="36"/>
+      <c r="N24" s="37"/>
+      <c r="O24" s="100"/>
+      <c r="P24" s="36"/>
+      <c r="Q24" s="37"/>
+      <c r="R24" s="30"/>
+      <c r="S24" s="30"/>
+      <c r="T24" s="31"/>
+      <c r="U24" s="32"/>
+      <c r="V24" s="32"/>
+      <c r="W24" s="32"/>
+      <c r="X24" s="32"/>
+      <c r="Y24" s="32"/>
+      <c r="Z24" s="32"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="106"/>
-      <c r="B25" s="40"/>
-      <c r="C25" s="107"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="107"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="113"/>
-      <c r="H25" s="39"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="113"/>
-      <c r="K25" s="40"/>
-      <c r="L25" s="110"/>
-      <c r="M25" s="39"/>
-      <c r="N25" s="40"/>
-      <c r="O25" s="110"/>
-      <c r="P25" s="39"/>
-      <c r="Q25" s="40"/>
-      <c r="R25" s="33"/>
-      <c r="S25" s="33"/>
-      <c r="T25" s="34"/>
-      <c r="U25" s="35"/>
-      <c r="V25" s="35"/>
-      <c r="W25" s="35"/>
-      <c r="X25" s="35"/>
-      <c r="Y25" s="35"/>
-      <c r="Z25" s="35"/>
+      <c r="A25" s="104"/>
+      <c r="B25" s="37"/>
+      <c r="C25" s="105"/>
+      <c r="D25" s="37"/>
+      <c r="E25" s="105"/>
+      <c r="F25" s="37"/>
+      <c r="G25" s="98"/>
+      <c r="H25" s="36"/>
+      <c r="I25" s="37"/>
+      <c r="J25" s="98"/>
+      <c r="K25" s="37"/>
+      <c r="L25" s="100"/>
+      <c r="M25" s="36"/>
+      <c r="N25" s="37"/>
+      <c r="O25" s="100"/>
+      <c r="P25" s="36"/>
+      <c r="Q25" s="37"/>
+      <c r="R25" s="30"/>
+      <c r="S25" s="30"/>
+      <c r="T25" s="31"/>
+      <c r="U25" s="32"/>
+      <c r="V25" s="32"/>
+      <c r="W25" s="32"/>
+      <c r="X25" s="32"/>
+      <c r="Y25" s="32"/>
+      <c r="Z25" s="32"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="106"/>
-      <c r="B26" s="40"/>
-      <c r="C26" s="107"/>
-      <c r="D26" s="40"/>
-      <c r="E26" s="107"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="113"/>
-      <c r="H26" s="39"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="113"/>
-      <c r="K26" s="40"/>
-      <c r="L26" s="110"/>
-      <c r="M26" s="39"/>
-      <c r="N26" s="40"/>
-      <c r="O26" s="110"/>
-      <c r="P26" s="39"/>
-      <c r="Q26" s="40"/>
-      <c r="R26" s="33"/>
-      <c r="S26" s="33"/>
-      <c r="T26" s="34"/>
-      <c r="U26" s="35"/>
-      <c r="V26" s="35"/>
-      <c r="W26" s="35"/>
-      <c r="X26" s="35"/>
-      <c r="Y26" s="35"/>
-      <c r="Z26" s="35"/>
+      <c r="A26" s="104"/>
+      <c r="B26" s="37"/>
+      <c r="C26" s="105"/>
+      <c r="D26" s="37"/>
+      <c r="E26" s="105"/>
+      <c r="F26" s="37"/>
+      <c r="G26" s="98"/>
+      <c r="H26" s="36"/>
+      <c r="I26" s="37"/>
+      <c r="J26" s="98"/>
+      <c r="K26" s="37"/>
+      <c r="L26" s="100"/>
+      <c r="M26" s="36"/>
+      <c r="N26" s="37"/>
+      <c r="O26" s="100"/>
+      <c r="P26" s="36"/>
+      <c r="Q26" s="37"/>
+      <c r="R26" s="30"/>
+      <c r="S26" s="30"/>
+      <c r="T26" s="31"/>
+      <c r="U26" s="32"/>
+      <c r="V26" s="32"/>
+      <c r="W26" s="32"/>
+      <c r="X26" s="32"/>
+      <c r="Y26" s="32"/>
+      <c r="Z26" s="32"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="106"/>
-      <c r="B27" s="40"/>
-      <c r="C27" s="107"/>
-      <c r="D27" s="40"/>
-      <c r="E27" s="107"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="113"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="113"/>
-      <c r="K27" s="40"/>
-      <c r="L27" s="110"/>
-      <c r="M27" s="39"/>
-      <c r="N27" s="40"/>
-      <c r="O27" s="110"/>
-      <c r="P27" s="39"/>
-      <c r="Q27" s="40"/>
-      <c r="R27" s="33"/>
-      <c r="S27" s="33"/>
-      <c r="T27" s="34"/>
-      <c r="U27" s="35"/>
-      <c r="V27" s="35"/>
-      <c r="W27" s="35"/>
-      <c r="X27" s="35"/>
-      <c r="Y27" s="35"/>
-      <c r="Z27" s="35"/>
+      <c r="A27" s="104"/>
+      <c r="B27" s="37"/>
+      <c r="C27" s="105"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="105"/>
+      <c r="F27" s="37"/>
+      <c r="G27" s="98"/>
+      <c r="H27" s="36"/>
+      <c r="I27" s="37"/>
+      <c r="J27" s="98"/>
+      <c r="K27" s="37"/>
+      <c r="L27" s="100"/>
+      <c r="M27" s="36"/>
+      <c r="N27" s="37"/>
+      <c r="O27" s="100"/>
+      <c r="P27" s="36"/>
+      <c r="Q27" s="37"/>
+      <c r="R27" s="30"/>
+      <c r="S27" s="30"/>
+      <c r="T27" s="31"/>
+      <c r="U27" s="32"/>
+      <c r="V27" s="32"/>
+      <c r="W27" s="32"/>
+      <c r="X27" s="32"/>
+      <c r="Y27" s="32"/>
+      <c r="Z27" s="32"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="106"/>
-      <c r="B28" s="40"/>
-      <c r="C28" s="107"/>
-      <c r="D28" s="40"/>
-      <c r="E28" s="107"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="113"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="113"/>
-      <c r="K28" s="40"/>
-      <c r="L28" s="110"/>
-      <c r="M28" s="39"/>
-      <c r="N28" s="40"/>
-      <c r="O28" s="110"/>
-      <c r="P28" s="39"/>
-      <c r="Q28" s="40"/>
-      <c r="R28" s="33"/>
-      <c r="S28" s="33"/>
-      <c r="T28" s="34"/>
-      <c r="U28" s="35"/>
-      <c r="V28" s="35"/>
-      <c r="W28" s="35"/>
-      <c r="X28" s="35"/>
-      <c r="Y28" s="35"/>
-      <c r="Z28" s="35"/>
+      <c r="A28" s="104"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="105"/>
+      <c r="D28" s="37"/>
+      <c r="E28" s="105"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="98"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="37"/>
+      <c r="J28" s="98"/>
+      <c r="K28" s="37"/>
+      <c r="L28" s="100"/>
+      <c r="M28" s="36"/>
+      <c r="N28" s="37"/>
+      <c r="O28" s="100"/>
+      <c r="P28" s="36"/>
+      <c r="Q28" s="37"/>
+      <c r="R28" s="30"/>
+      <c r="S28" s="30"/>
+      <c r="T28" s="31"/>
+      <c r="U28" s="32"/>
+      <c r="V28" s="32"/>
+      <c r="W28" s="32"/>
+      <c r="X28" s="32"/>
+      <c r="Y28" s="32"/>
+      <c r="Z28" s="32"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="106"/>
-      <c r="B29" s="40"/>
-      <c r="C29" s="107"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="107"/>
-      <c r="F29" s="40"/>
-      <c r="G29" s="113"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="40"/>
-      <c r="J29" s="113"/>
-      <c r="K29" s="40"/>
-      <c r="L29" s="110"/>
-      <c r="M29" s="39"/>
-      <c r="N29" s="40"/>
-      <c r="O29" s="110"/>
-      <c r="P29" s="39"/>
-      <c r="Q29" s="40"/>
-      <c r="R29" s="33"/>
-      <c r="S29" s="33"/>
-      <c r="T29" s="34"/>
-      <c r="U29" s="35"/>
-      <c r="V29" s="35"/>
-      <c r="W29" s="35"/>
-      <c r="X29" s="35"/>
-      <c r="Y29" s="35"/>
-      <c r="Z29" s="35"/>
+      <c r="A29" s="104"/>
+      <c r="B29" s="37"/>
+      <c r="C29" s="105"/>
+      <c r="D29" s="37"/>
+      <c r="E29" s="105"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="98"/>
+      <c r="H29" s="36"/>
+      <c r="I29" s="37"/>
+      <c r="J29" s="98"/>
+      <c r="K29" s="37"/>
+      <c r="L29" s="100"/>
+      <c r="M29" s="36"/>
+      <c r="N29" s="37"/>
+      <c r="O29" s="100"/>
+      <c r="P29" s="36"/>
+      <c r="Q29" s="37"/>
+      <c r="R29" s="30"/>
+      <c r="S29" s="30"/>
+      <c r="T29" s="31"/>
+      <c r="U29" s="32"/>
+      <c r="V29" s="32"/>
+      <c r="W29" s="32"/>
+      <c r="X29" s="32"/>
+      <c r="Y29" s="32"/>
+      <c r="Z29" s="32"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="106"/>
-      <c r="B30" s="40"/>
-      <c r="C30" s="107"/>
-      <c r="D30" s="40"/>
-      <c r="E30" s="107"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="113"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="40"/>
-      <c r="J30" s="113"/>
-      <c r="K30" s="40"/>
-      <c r="L30" s="110"/>
-      <c r="M30" s="39"/>
-      <c r="N30" s="40"/>
-      <c r="O30" s="110"/>
-      <c r="P30" s="39"/>
-      <c r="Q30" s="40"/>
-      <c r="R30" s="33"/>
-      <c r="S30" s="33"/>
-      <c r="T30" s="34"/>
-      <c r="U30" s="35"/>
-      <c r="V30" s="35"/>
-      <c r="W30" s="35"/>
-      <c r="X30" s="35"/>
-      <c r="Y30" s="35"/>
-      <c r="Z30" s="35"/>
+      <c r="A30" s="104"/>
+      <c r="B30" s="37"/>
+      <c r="C30" s="105"/>
+      <c r="D30" s="37"/>
+      <c r="E30" s="105"/>
+      <c r="F30" s="37"/>
+      <c r="G30" s="98"/>
+      <c r="H30" s="36"/>
+      <c r="I30" s="37"/>
+      <c r="J30" s="98"/>
+      <c r="K30" s="37"/>
+      <c r="L30" s="100"/>
+      <c r="M30" s="36"/>
+      <c r="N30" s="37"/>
+      <c r="O30" s="100"/>
+      <c r="P30" s="36"/>
+      <c r="Q30" s="37"/>
+      <c r="R30" s="30"/>
+      <c r="S30" s="30"/>
+      <c r="T30" s="31"/>
+      <c r="U30" s="32"/>
+      <c r="V30" s="32"/>
+      <c r="W30" s="32"/>
+      <c r="X30" s="32"/>
+      <c r="Y30" s="32"/>
+      <c r="Z30" s="32"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="108"/>
-      <c r="B31" s="97"/>
-      <c r="C31" s="109"/>
-      <c r="D31" s="97"/>
-      <c r="E31" s="109"/>
-      <c r="F31" s="97"/>
-      <c r="G31" s="116"/>
-      <c r="H31" s="90"/>
-      <c r="I31" s="97"/>
-      <c r="J31" s="116"/>
-      <c r="K31" s="97"/>
-      <c r="L31" s="111"/>
-      <c r="M31" s="90"/>
-      <c r="N31" s="97"/>
-      <c r="O31" s="111"/>
-      <c r="P31" s="90"/>
-      <c r="Q31" s="97"/>
-      <c r="R31" s="36"/>
-      <c r="S31" s="36"/>
-      <c r="T31" s="37"/>
-      <c r="U31" s="35"/>
-      <c r="V31" s="35"/>
-      <c r="W31" s="35"/>
-      <c r="X31" s="35"/>
-      <c r="Y31" s="35"/>
-      <c r="Z31" s="35"/>
+      <c r="A31" s="107"/>
+      <c r="B31" s="90"/>
+      <c r="C31" s="108"/>
+      <c r="D31" s="90"/>
+      <c r="E31" s="108"/>
+      <c r="F31" s="90"/>
+      <c r="G31" s="99"/>
+      <c r="H31" s="89"/>
+      <c r="I31" s="90"/>
+      <c r="J31" s="99"/>
+      <c r="K31" s="90"/>
+      <c r="L31" s="101"/>
+      <c r="M31" s="89"/>
+      <c r="N31" s="90"/>
+      <c r="O31" s="101"/>
+      <c r="P31" s="89"/>
+      <c r="Q31" s="90"/>
+      <c r="R31" s="33"/>
+      <c r="S31" s="33"/>
+      <c r="T31" s="34"/>
+      <c r="U31" s="32"/>
+      <c r="V31" s="32"/>
+      <c r="W31" s="32"/>
+      <c r="X31" s="32"/>
+      <c r="Y31" s="32"/>
+      <c r="Z31" s="32"/>
     </row>
     <row r="32" spans="1:26" ht="12.75" customHeight="1">
       <c r="D32" s="3"/>
@@ -10486,62 +10830,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -10566,62 +10910,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/詳細設計図/メニュー画面_詳細設計図.xlsx
+++ b/詳細設計図/メニュー画面_詳細設計図.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-04\Documents\project\MyTaskSystem\詳細設計図\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-04\Documents\プロジェクト演習\詳細設計図\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{830F4CCE-EB8F-4392-9C89-FFBE73930675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{249644D2-D8BD-4876-A667-28D01F274C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="10245" windowHeight="10920" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -25,12 +25,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="91">
   <si>
     <t>プロジェクト型演習　成果ドキュメント</t>
-  </si>
-  <si>
-    <t>○○○○システム</t>
   </si>
   <si>
     <t>初版</t>
@@ -232,25 +229,7 @@
 エラーの原因がユーザ名が未入力である旨通知する</t>
   </si>
   <si>
-    <t>ログイン</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>ログインをする</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>ユーザー</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>未ログイン状態</t>
-    <rPh sb="0" eb="1">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ジョウタイ</t>
-    </rPh>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -261,93 +240,6 @@
     <t>志賀</t>
     <rPh sb="0" eb="2">
       <t>シガ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>1.ユーザーはログイン状態になっている
-2.ユーザーは[メニュー画面]に遷移している
-3.ユーザーのセッションが有効になっている</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t xml:space="preserve">①ユーザーはユーザーIDとパスワードを入力する
-②ユーザーは「ログイン」ボタンを押下(Alt-1)
-③システムはユーザーIDに該当するユーザーの情報を取得(Alt-2)
-④システムは該当したユーザーのパスワードが入力されたパスワードと一致するか認証(Alt-3)
-⑤システムはユーザーを認証し、ログイン状態に
-⑥システムは画面を[ログイン画面]から[メニュー画面]に遷移
-</t>
-    <rPh sb="19" eb="21">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="40" eb="42">
-      <t>オウカ</t>
-    </rPh>
-    <rPh sb="63" eb="65">
-      <t>ガイトウ</t>
-    </rPh>
-    <rPh sb="72" eb="74">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="75" eb="77">
-      <t>シュトク</t>
-    </rPh>
-    <rPh sb="91" eb="93">
-      <t>ガイトウ</t>
-    </rPh>
-    <rPh sb="106" eb="108">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="117" eb="119">
-      <t>イッチ</t>
-    </rPh>
-    <rPh sb="122" eb="124">
-      <t>ニンショウ</t>
-    </rPh>
-    <rPh sb="143" eb="145">
-      <t>ニンショウ</t>
-    </rPh>
-    <rPh sb="151" eb="153">
-      <t>ジョウタイ</t>
-    </rPh>
-    <rPh sb="161" eb="163">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="169" eb="171">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="179" eb="181">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="183" eb="185">
-      <t>センイ</t>
-    </rPh>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>Alt-1:ユーザーIDまたはパスワードが入力されなかった場合
-1①に戻る
-2.・ユーザーIDが入力されなかった場合「ユーザーIDを入力してください」というエラーメッセージを表示
-・パスワードが入力されなかった場合「パスワードを入力してください」というエラーメッセージを表示
-・両方が入力されなかった場合「ユーザーIDとパスワードを入力してください」というエラーメッセージを表示
-Alt-2:ユーザーIDに該当するユーザーの情報が存在しない場合
-1.メインフロー1に戻る
-2.「ログイン認証に失敗しました」というエラーメッセージを表示
-Alt-3:パスワードが一致しなかった場合
-1.メインフロー1に戻る
-2.「ログイン認証に失敗しました」というエラーメッセージを表示</t>
-    <rPh sb="66" eb="68">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="114" eb="116">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="139" eb="141">
-      <t>リョウホウ</t>
-    </rPh>
-    <rPh sb="166" eb="168">
-      <t>ニュウリョク</t>
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
@@ -442,11 +334,71 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>task-list.jsp</t>
+    <t>logout.jsp</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>logout.jsp</t>
+    <t>メニュー</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>メニューを表示</t>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>ログイン状態</t>
+    <rPh sb="4" eb="6">
+      <t>ジョウタイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>1.目的先へ遷移</t>
+    <rPh sb="2" eb="4">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>サキ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>センイ</t>
+    </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>TaskListServlet</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+①タスク登録ボタン/タスク一覧ボタン/ログアウトボタンを表示
+②ユーザーが目的のボタンを押下
+③目的先へ遷移
+</t>
+    <rPh sb="5" eb="7">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>イチラン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>モクテキ</t>
+    </rPh>
+    <rPh sb="45" eb="47">
+      <t>オウカ</t>
+    </rPh>
+    <rPh sb="49" eb="52">
+      <t>モクテキサキ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>センイ</t>
+    </rPh>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1555,7 +1507,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1661,6 +1613,24 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1685,6 +1655,96 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1700,99 +1760,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1814,32 +1784,143 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1847,143 +1928,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="72" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="85" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="86" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2263,85 +2212,85 @@
   <sheetData>
     <row r="1" spans="3:16" ht="30" customHeight="1"/>
     <row r="2" spans="3:16" ht="30" customHeight="1">
-      <c r="C2" s="40" t="s">
+      <c r="C2" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
-      <c r="M2" s="41"/>
-      <c r="N2" s="41"/>
-      <c r="O2" s="41"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
       <c r="P2" s="1"/>
     </row>
     <row r="3" spans="3:16" ht="30" customHeight="1">
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="39"/>
-      <c r="G3" s="39"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39"/>
-      <c r="K3" s="39"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="39"/>
-      <c r="O3" s="39"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="45"/>
+      <c r="G3" s="45"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="45"/>
+      <c r="O3" s="45"/>
       <c r="P3" s="1"/>
     </row>
     <row r="4" spans="3:16" ht="30" customHeight="1">
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="39"/>
-      <c r="M4" s="39"/>
-      <c r="N4" s="39"/>
-      <c r="O4" s="39"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="45"/>
+      <c r="G4" s="45"/>
+      <c r="H4" s="45"/>
+      <c r="I4" s="45"/>
+      <c r="J4" s="45"/>
+      <c r="K4" s="45"/>
+      <c r="L4" s="45"/>
+      <c r="M4" s="45"/>
+      <c r="N4" s="45"/>
+      <c r="O4" s="45"/>
       <c r="P4" s="1"/>
     </row>
     <row r="5" spans="3:16" ht="30" customHeight="1">
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39"/>
-      <c r="K5" s="39"/>
-      <c r="L5" s="39"/>
-      <c r="M5" s="39"/>
-      <c r="N5" s="39"/>
-      <c r="O5" s="39"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="45"/>
+      <c r="I5" s="45"/>
+      <c r="J5" s="45"/>
+      <c r="K5" s="45"/>
+      <c r="L5" s="45"/>
+      <c r="M5" s="45"/>
+      <c r="N5" s="45"/>
+      <c r="O5" s="45"/>
       <c r="P5" s="1"/>
     </row>
     <row r="6" spans="3:16" ht="30" customHeight="1">
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
-      <c r="F6" s="39"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="39"/>
-      <c r="I6" s="39"/>
-      <c r="J6" s="39"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="39"/>
-      <c r="M6" s="39"/>
-      <c r="N6" s="39"/>
-      <c r="O6" s="39"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="45"/>
+      <c r="M6" s="45"/>
+      <c r="N6" s="45"/>
+      <c r="O6" s="45"/>
       <c r="P6" s="1"/>
     </row>
     <row r="7" spans="3:16" ht="30" customHeight="1">
@@ -2361,46 +2310,46 @@
       <c r="P7" s="1"/>
     </row>
     <row r="8" spans="3:16" ht="30" customHeight="1">
-      <c r="E8" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="39"/>
-      <c r="K8" s="39"/>
-      <c r="L8" s="39"/>
-      <c r="M8" s="39"/>
+      <c r="E8" s="48" t="s">
+        <v>67</v>
+      </c>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="45"/>
+      <c r="K8" s="45"/>
+      <c r="L8" s="45"/>
+      <c r="M8" s="45"/>
     </row>
     <row r="9" spans="3:16" ht="30" customHeight="1"/>
     <row r="10" spans="3:16" ht="30" customHeight="1"/>
     <row r="11" spans="3:16" ht="30" customHeight="1"/>
     <row r="12" spans="3:16" ht="30" customHeight="1"/>
     <row r="13" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G13" s="35" t="s">
+      <c r="G13" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="43"/>
+      <c r="I13" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="37"/>
-      <c r="I13" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="J13" s="36"/>
-      <c r="K13" s="37"/>
+      <c r="J13" s="42"/>
+      <c r="K13" s="43"/>
     </row>
     <row r="14" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G14" s="35"/>
-      <c r="H14" s="37"/>
-      <c r="I14" s="35"/>
-      <c r="J14" s="36"/>
-      <c r="K14" s="37"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="43"/>
     </row>
     <row r="15" spans="3:16" ht="15.75" customHeight="1">
-      <c r="G15" s="35"/>
-      <c r="H15" s="37"/>
-      <c r="I15" s="35"/>
-      <c r="J15" s="36"/>
-      <c r="K15" s="37"/>
+      <c r="G15" s="41"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="41"/>
+      <c r="J15" s="42"/>
+      <c r="K15" s="43"/>
     </row>
     <row r="16" spans="3:16" ht="15.75" customHeight="1">
       <c r="G16" s="3"/>
@@ -2409,13 +2358,13 @@
       <c r="J16" s="3"/>
     </row>
     <row r="17" spans="7:11" ht="30" customHeight="1">
-      <c r="G17" s="38" t="s">
-        <v>4</v>
-      </c>
-      <c r="H17" s="39"/>
-      <c r="I17" s="39"/>
-      <c r="J17" s="39"/>
-      <c r="K17" s="39"/>
+      <c r="G17" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="H17" s="45"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="45"/>
+      <c r="K17" s="45"/>
     </row>
     <row r="18" spans="7:11" ht="14.25" customHeight="1"/>
     <row r="19" spans="7:11" ht="24.75" customHeight="1"/>
@@ -3429,212 +3378,210 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="62" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="79" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="43" t="s">
+      <c r="E1" s="80"/>
+      <c r="F1" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="44"/>
-      <c r="F1" s="43" t="s">
+      <c r="G1" s="80"/>
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="44"/>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="6" t="s">
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="65"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="81" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" s="82"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="84">
+        <v>45705</v>
+      </c>
+      <c r="I2" s="75" t="s">
+        <v>68</v>
+      </c>
+      <c r="J2" s="77"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="65"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="78"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1">
+      <c r="A4" s="65"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="78"/>
+    </row>
+    <row r="5" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A5" s="68" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="64"/>
-      <c r="B2" s="39"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="E2" s="46"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="49">
-        <v>45705</v>
-      </c>
-      <c r="I2" s="51" t="s">
-        <v>72</v>
-      </c>
-      <c r="J2" s="52"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="64"/>
-      <c r="B3" s="39"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="53"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="64"/>
-      <c r="B4" s="65"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="53"/>
-    </row>
-    <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="66" t="s">
+      <c r="B5" s="53"/>
+      <c r="C5" s="69"/>
+      <c r="D5" s="52" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="53"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="53"/>
+      <c r="J5" s="54"/>
+    </row>
+    <row r="6" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A6" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="67"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="74" t="s">
-        <v>67</v>
-      </c>
-      <c r="E5" s="67"/>
-      <c r="F5" s="67"/>
-      <c r="G5" s="67"/>
-      <c r="H5" s="67"/>
-      <c r="I5" s="67"/>
-      <c r="J5" s="75"/>
-    </row>
-    <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="55" t="s">
+      <c r="B6" s="42"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="55" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="56"/>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A7" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="36"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="76" t="s">
-        <v>68</v>
-      </c>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="57"/>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="55" t="s">
+      <c r="B7" s="42"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="55" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="56"/>
+    </row>
+    <row r="8" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A8" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="76" t="s">
-        <v>69</v>
-      </c>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="57"/>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="55" t="s">
+      <c r="B8" s="42"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="55" t="s">
+        <v>87</v>
+      </c>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="56"/>
+    </row>
+    <row r="9" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A9" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="36"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="76" t="s">
-        <v>70</v>
-      </c>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="36"/>
-      <c r="H8" s="36"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="57"/>
-    </row>
-    <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="69" t="s">
+      <c r="B9" s="74" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="54" t="s">
+      <c r="C9" s="43"/>
+      <c r="D9" s="57" t="s">
+        <v>90</v>
+      </c>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
+      <c r="I9" s="58"/>
+      <c r="J9" s="59"/>
+    </row>
+    <row r="10" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A10" s="72"/>
+      <c r="B10" s="74" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="37"/>
-      <c r="D9" s="56" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" s="77"/>
-      <c r="F9" s="77"/>
-      <c r="G9" s="77"/>
-      <c r="H9" s="77"/>
-      <c r="I9" s="77"/>
-      <c r="J9" s="78"/>
-    </row>
-    <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="70"/>
-      <c r="B10" s="54" t="s">
+      <c r="C10" s="43"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="56"/>
+    </row>
+    <row r="11" spans="1:10" ht="64.5" customHeight="1">
+      <c r="A11" s="73"/>
+      <c r="B11" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="37"/>
-      <c r="D10" s="56" t="s">
-        <v>75</v>
-      </c>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
-      <c r="G10" s="36"/>
-      <c r="H10" s="36"/>
-      <c r="I10" s="36"/>
-      <c r="J10" s="57"/>
-    </row>
-    <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="71"/>
-      <c r="B11" s="54" t="s">
+      <c r="C11" s="43"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="56"/>
+    </row>
+    <row r="12" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A12" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="37"/>
-      <c r="D11" s="56"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="36"/>
-      <c r="G11" s="36"/>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
-      <c r="J11" s="57"/>
-    </row>
-    <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="55" t="s">
+      <c r="B12" s="42"/>
+      <c r="C12" s="43"/>
+      <c r="D12" s="57" t="s">
+        <v>88</v>
+      </c>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="56"/>
+    </row>
+    <row r="13" spans="1:10" ht="26.25" customHeight="1">
+      <c r="A13" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="36"/>
-      <c r="C12" s="37"/>
-      <c r="D12" s="56" t="s">
-        <v>73</v>
-      </c>
-      <c r="E12" s="36"/>
-      <c r="F12" s="36"/>
-      <c r="G12" s="36"/>
-      <c r="H12" s="36"/>
-      <c r="I12" s="36"/>
-      <c r="J12" s="57"/>
-    </row>
-    <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="58" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="59"/>
-      <c r="C13" s="60"/>
-      <c r="D13" s="72"/>
-      <c r="E13" s="59"/>
-      <c r="F13" s="59"/>
-      <c r="G13" s="59"/>
-      <c r="H13" s="59"/>
-      <c r="I13" s="59"/>
-      <c r="J13" s="73"/>
+      <c r="B13" s="50"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+      <c r="G13" s="50"/>
+      <c r="H13" s="50"/>
+      <c r="I13" s="50"/>
+      <c r="J13" s="51"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4625,6 +4572,25 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A1:C4"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A7:C7"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A9:A11"/>
+    <mergeCell ref="B9:C9"/>
     <mergeCell ref="D13:J13"/>
     <mergeCell ref="D5:J5"/>
     <mergeCell ref="D6:J6"/>
@@ -4633,25 +4599,6 @@
     <mergeCell ref="D9:J9"/>
     <mergeCell ref="D10:J10"/>
     <mergeCell ref="D11:J11"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A1:C4"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A6:C6"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A9:A11"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4670,64 +4617,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="81" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="43" t="s">
+      <c r="A1" s="87" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="79" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="80"/>
+      <c r="F1" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="44"/>
-      <c r="F1" s="43" t="s">
+      <c r="G1" s="80"/>
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="44"/>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="64"/>
-      <c r="B2" s="39"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="52"/>
+      <c r="A2" s="65"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="77"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="64"/>
-      <c r="B3" s="39"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="53"/>
+      <c r="A3" s="65"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="78"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="82"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="79"/>
-      <c r="I4" s="79"/>
-      <c r="J4" s="80"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="91"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="86"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -6083,64 +6030,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="81" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="43" t="s">
+      <c r="A1" s="87" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="63"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="79" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="80"/>
+      <c r="F1" s="79" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="44"/>
-      <c r="F1" s="43" t="s">
+      <c r="G1" s="80"/>
+      <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="44"/>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="7" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="64"/>
-      <c r="B2" s="39"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="45"/>
-      <c r="E2" s="46"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="51"/>
-      <c r="I2" s="51"/>
-      <c r="J2" s="52"/>
+      <c r="A2" s="65"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="75"/>
+      <c r="I2" s="75"/>
+      <c r="J2" s="77"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="64"/>
-      <c r="B3" s="39"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="53"/>
+      <c r="A3" s="65"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="78"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="82"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="79"/>
-      <c r="I4" s="79"/>
-      <c r="J4" s="80"/>
+      <c r="A4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="90"/>
+      <c r="D4" s="91"/>
+      <c r="E4" s="90"/>
+      <c r="F4" s="91"/>
+      <c r="G4" s="90"/>
+      <c r="H4" s="85"/>
+      <c r="I4" s="85"/>
+      <c r="J4" s="86"/>
     </row>
     <row r="5" spans="1:10" ht="12.75" customHeight="1">
       <c r="A5" s="8"/>
@@ -7490,436 +7437,436 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="118" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="119"/>
+      <c r="C1" s="120"/>
+      <c r="D1" s="122" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="69"/>
+      <c r="F1" s="122" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" s="69"/>
+      <c r="H1" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="37" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="18" customHeight="1">
+      <c r="A2" s="108"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="81" t="s">
+        <v>67</v>
+      </c>
+      <c r="E2" s="82"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="84">
+        <v>45707</v>
+      </c>
+      <c r="I2" s="75" t="s">
+        <v>68</v>
+      </c>
+      <c r="J2" s="116"/>
+    </row>
+    <row r="3" spans="1:10" ht="18" customHeight="1">
+      <c r="A3" s="108"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="66"/>
+      <c r="F3" s="83"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="76"/>
+      <c r="I3" s="76"/>
+      <c r="J3" s="117"/>
+    </row>
+    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
+      <c r="A4" s="108"/>
+      <c r="B4" s="45"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="66"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="66"/>
+      <c r="H4" s="76"/>
+      <c r="I4" s="76"/>
+      <c r="J4" s="117"/>
+    </row>
+    <row r="5" spans="1:10" ht="28.5" customHeight="1">
+      <c r="A5" s="121" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="115"/>
-      <c r="C1" s="116"/>
-      <c r="D1" s="117" t="s">
-        <v>6</v>
-      </c>
-      <c r="E1" s="68"/>
-      <c r="F1" s="117" t="s">
-        <v>7</v>
-      </c>
-      <c r="G1" s="68"/>
-      <c r="H1" s="118" t="s">
-        <v>8</v>
-      </c>
-      <c r="I1" s="119" t="s">
-        <v>9</v>
-      </c>
-      <c r="J1" s="120" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="121"/>
-      <c r="B2" s="112"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="45" t="s">
+      <c r="B5" s="103"/>
+      <c r="C5" s="80"/>
+      <c r="D5" s="102" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" s="103"/>
+      <c r="F5" s="103"/>
+      <c r="G5" s="103"/>
+      <c r="H5" s="103"/>
+      <c r="I5" s="103"/>
+      <c r="J5" s="104"/>
+    </row>
+    <row r="6" spans="1:10" ht="21" customHeight="1">
+      <c r="A6" s="95" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="56"/>
+    </row>
+    <row r="7" spans="1:10" ht="21" customHeight="1">
+      <c r="A7" s="105"/>
+      <c r="B7" s="106"/>
+      <c r="C7" s="106"/>
+      <c r="D7" s="106"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="106"/>
+      <c r="G7" s="106"/>
+      <c r="H7" s="106"/>
+      <c r="I7" s="106"/>
+      <c r="J7" s="107"/>
+    </row>
+    <row r="8" spans="1:10" ht="21" customHeight="1">
+      <c r="A8" s="108"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="109"/>
+    </row>
+    <row r="9" spans="1:10" ht="21" customHeight="1">
+      <c r="A9" s="108"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="45"/>
+      <c r="F9" s="45"/>
+      <c r="G9" s="45"/>
+      <c r="H9" s="45"/>
+      <c r="I9" s="45"/>
+      <c r="J9" s="109"/>
+    </row>
+    <row r="10" spans="1:10" ht="21" customHeight="1">
+      <c r="A10" s="108"/>
+      <c r="B10" s="45"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="45"/>
+      <c r="F10" s="45"/>
+      <c r="G10" s="45"/>
+      <c r="H10" s="45"/>
+      <c r="I10" s="45"/>
+      <c r="J10" s="109"/>
+    </row>
+    <row r="11" spans="1:10" ht="21" customHeight="1">
+      <c r="A11" s="108"/>
+      <c r="B11" s="45"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="45"/>
+      <c r="I11" s="45"/>
+      <c r="J11" s="109"/>
+    </row>
+    <row r="12" spans="1:10" ht="21" customHeight="1">
+      <c r="A12" s="108"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="109"/>
+    </row>
+    <row r="13" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A13" s="110"/>
+      <c r="B13" s="111"/>
+      <c r="C13" s="111"/>
+      <c r="D13" s="111"/>
+      <c r="E13" s="111"/>
+      <c r="F13" s="111"/>
+      <c r="G13" s="111"/>
+      <c r="H13" s="111"/>
+      <c r="I13" s="111"/>
+      <c r="J13" s="112"/>
+    </row>
+    <row r="14" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A14" s="113" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="114"/>
+      <c r="C14" s="114"/>
+      <c r="D14" s="114"/>
+      <c r="E14" s="114"/>
+      <c r="F14" s="114"/>
+      <c r="G14" s="114"/>
+      <c r="H14" s="114"/>
+      <c r="I14" s="114"/>
+      <c r="J14" s="115"/>
+    </row>
+    <row r="15" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A15" s="95" t="s">
+        <v>26</v>
+      </c>
+      <c r="B15" s="42"/>
+      <c r="C15" s="43"/>
+      <c r="D15" s="55" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="J15" s="38" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A16" s="95" t="s">
+        <v>28</v>
+      </c>
+      <c r="B16" s="42"/>
+      <c r="C16" s="43"/>
+      <c r="D16" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F16" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H16" s="96" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" s="42"/>
+      <c r="J16" s="56"/>
+    </row>
+    <row r="17" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A17" s="92" t="s">
         <v>71</v>
       </c>
-      <c r="E2" s="46"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="46"/>
-      <c r="H2" s="49">
-        <v>45707</v>
-      </c>
-      <c r="I2" s="51" t="s">
-        <v>72</v>
-      </c>
-      <c r="J2" s="122"/>
-    </row>
-    <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="121"/>
-      <c r="B3" s="112"/>
-      <c r="C3" s="48"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="48"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="50"/>
-      <c r="I3" s="50"/>
-      <c r="J3" s="123"/>
-    </row>
-    <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="121"/>
-      <c r="B4" s="112"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="48"/>
-      <c r="H4" s="50"/>
-      <c r="I4" s="50"/>
-      <c r="J4" s="123"/>
-    </row>
-    <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="124" t="s">
-        <v>24</v>
-      </c>
-      <c r="B5" s="88"/>
-      <c r="C5" s="44"/>
-      <c r="D5" s="91" t="s">
-        <v>88</v>
-      </c>
-      <c r="E5" s="88"/>
-      <c r="F5" s="88"/>
-      <c r="G5" s="88"/>
-      <c r="H5" s="88"/>
-      <c r="I5" s="88"/>
-      <c r="J5" s="125"/>
-    </row>
-    <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="126" t="s">
-        <v>25</v>
-      </c>
-      <c r="B6" s="36"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="36"/>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="57"/>
-    </row>
-    <row r="7" spans="1:10" ht="21" customHeight="1">
-      <c r="A7" s="127"/>
-      <c r="B7" s="94"/>
-      <c r="C7" s="94"/>
-      <c r="D7" s="94"/>
-      <c r="E7" s="94"/>
-      <c r="F7" s="94"/>
-      <c r="G7" s="94"/>
-      <c r="H7" s="94"/>
-      <c r="I7" s="94"/>
-      <c r="J7" s="128"/>
-    </row>
-    <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="121"/>
-      <c r="B8" s="112"/>
-      <c r="C8" s="112"/>
-      <c r="D8" s="112"/>
-      <c r="E8" s="112"/>
-      <c r="F8" s="112"/>
-      <c r="G8" s="112"/>
-      <c r="H8" s="112"/>
-      <c r="I8" s="112"/>
-      <c r="J8" s="129"/>
-    </row>
-    <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="121"/>
-      <c r="B9" s="112"/>
-      <c r="C9" s="112"/>
-      <c r="D9" s="112"/>
-      <c r="E9" s="112"/>
-      <c r="F9" s="112"/>
-      <c r="G9" s="112"/>
-      <c r="H9" s="112"/>
-      <c r="I9" s="112"/>
-      <c r="J9" s="129"/>
-    </row>
-    <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="121"/>
-      <c r="B10" s="112"/>
-      <c r="C10" s="112"/>
-      <c r="D10" s="112"/>
-      <c r="E10" s="112"/>
-      <c r="F10" s="112"/>
-      <c r="G10" s="112"/>
-      <c r="H10" s="112"/>
-      <c r="I10" s="112"/>
-      <c r="J10" s="129"/>
-    </row>
-    <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="121"/>
-      <c r="B11" s="112"/>
-      <c r="C11" s="112"/>
-      <c r="D11" s="112"/>
-      <c r="E11" s="112"/>
-      <c r="F11" s="112"/>
-      <c r="G11" s="112"/>
-      <c r="H11" s="112"/>
-      <c r="I11" s="112"/>
-      <c r="J11" s="129"/>
-    </row>
-    <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="121"/>
-      <c r="B12" s="112"/>
-      <c r="C12" s="112"/>
-      <c r="D12" s="112"/>
-      <c r="E12" s="112"/>
-      <c r="F12" s="112"/>
-      <c r="G12" s="112"/>
-      <c r="H12" s="112"/>
-      <c r="I12" s="112"/>
-      <c r="J12" s="129"/>
-    </row>
-    <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="130"/>
-      <c r="B13" s="113"/>
-      <c r="C13" s="113"/>
-      <c r="D13" s="113"/>
-      <c r="E13" s="113"/>
-      <c r="F13" s="113"/>
-      <c r="G13" s="113"/>
-      <c r="H13" s="113"/>
-      <c r="I13" s="113"/>
-      <c r="J13" s="131"/>
-    </row>
-    <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="132" t="s">
-        <v>26</v>
-      </c>
-      <c r="B14" s="111"/>
-      <c r="C14" s="111"/>
-      <c r="D14" s="111"/>
-      <c r="E14" s="111"/>
-      <c r="F14" s="111"/>
-      <c r="G14" s="111"/>
-      <c r="H14" s="111"/>
-      <c r="I14" s="111"/>
-      <c r="J14" s="133"/>
-    </row>
-    <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="36"/>
-      <c r="C15" s="37"/>
-      <c r="D15" s="76" t="s">
-        <v>89</v>
-      </c>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="37"/>
-      <c r="I15" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="J15" s="134" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="126" t="s">
-        <v>29</v>
-      </c>
-      <c r="B16" s="36"/>
-      <c r="C16" s="37"/>
-      <c r="D16" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G16" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="H16" s="97" t="s">
-        <v>20</v>
-      </c>
-      <c r="I16" s="36"/>
-      <c r="J16" s="57"/>
-    </row>
-    <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="135" t="s">
-        <v>78</v>
-      </c>
-      <c r="B17" s="36"/>
-      <c r="C17" s="37"/>
+      <c r="B17" s="42"/>
+      <c r="C17" s="43"/>
       <c r="D17" s="16"/>
       <c r="E17" s="16" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F17" s="17" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="H17" s="76" t="s">
-        <v>85</v>
-      </c>
-      <c r="I17" s="36"/>
-      <c r="J17" s="57"/>
+        <v>75</v>
+      </c>
+      <c r="H17" s="55" t="s">
+        <v>78</v>
+      </c>
+      <c r="I17" s="42"/>
+      <c r="J17" s="56"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="126" t="s">
+      <c r="A18" s="95" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" s="42"/>
+      <c r="C18" s="42"/>
+      <c r="D18" s="42"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="42"/>
+      <c r="H18" s="42"/>
+      <c r="I18" s="42"/>
+      <c r="J18" s="56"/>
+    </row>
+    <row r="19" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A19" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="36"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="36"/>
-      <c r="G18" s="36"/>
-      <c r="H18" s="36"/>
-      <c r="I18" s="36"/>
-      <c r="J18" s="57"/>
-    </row>
-    <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="126" t="s">
+      <c r="B19" s="42"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="55" t="s">
+        <v>89</v>
+      </c>
+      <c r="E19" s="42"/>
+      <c r="F19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="36"/>
-      <c r="C19" s="37"/>
-      <c r="D19" s="76" t="s">
-        <v>91</v>
-      </c>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
-      <c r="G19" s="36"/>
-      <c r="H19" s="37"/>
-      <c r="I19" s="15" t="s">
+      <c r="J19" s="38" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A20" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="J19" s="134" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="126" t="s">
+      <c r="B20" s="42"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="36"/>
-      <c r="C20" s="37"/>
-      <c r="D20" s="15" t="s">
+      <c r="E20" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="F20" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="F20" s="15" t="s">
+      <c r="G20" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="G20" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="H20" s="97" t="s">
-        <v>20</v>
-      </c>
-      <c r="I20" s="36"/>
-      <c r="J20" s="57"/>
+      <c r="H20" s="96" t="s">
+        <v>19</v>
+      </c>
+      <c r="I20" s="42"/>
+      <c r="J20" s="56"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="135" t="s">
-        <v>79</v>
-      </c>
-      <c r="B21" s="109"/>
-      <c r="C21" s="110"/>
+      <c r="A21" s="92" t="s">
+        <v>72</v>
+      </c>
+      <c r="B21" s="93"/>
+      <c r="C21" s="94"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F21" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" s="55" t="s">
+        <v>79</v>
+      </c>
+      <c r="I21" s="58"/>
+      <c r="J21" s="59"/>
+    </row>
+    <row r="22" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A22" s="95" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" s="42"/>
+      <c r="C22" s="42"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="42"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="42"/>
+      <c r="J22" s="56"/>
+    </row>
+    <row r="23" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A23" s="95" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" s="42"/>
+      <c r="C23" s="43"/>
+      <c r="D23" s="55" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="J23" s="38" t="s">
         <v>83</v>
       </c>
-      <c r="G21" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="H21" s="76" t="s">
-        <v>86</v>
-      </c>
-      <c r="I21" s="77"/>
-      <c r="J21" s="78"/>
-    </row>
-    <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="126" t="s">
-        <v>26</v>
-      </c>
-      <c r="B22" s="36"/>
-      <c r="C22" s="36"/>
-      <c r="D22" s="36"/>
-      <c r="E22" s="36"/>
-      <c r="F22" s="36"/>
-      <c r="G22" s="36"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="57"/>
-    </row>
-    <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="126" t="s">
-        <v>27</v>
-      </c>
-      <c r="B23" s="36"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="76" t="s">
-        <v>92</v>
-      </c>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="36"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="15" t="s">
+    </row>
+    <row r="24" spans="1:10" ht="19.5" customHeight="1">
+      <c r="A24" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="J23" s="134" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="126" t="s">
+      <c r="B24" s="42"/>
+      <c r="C24" s="43"/>
+      <c r="D24" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="36"/>
-      <c r="C24" s="37"/>
-      <c r="D24" s="15" t="s">
+      <c r="E24" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="F24" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="F24" s="15" t="s">
+      <c r="G24" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="G24" s="15" t="s">
-        <v>33</v>
-      </c>
-      <c r="H24" s="97" t="s">
-        <v>20</v>
-      </c>
-      <c r="I24" s="36"/>
-      <c r="J24" s="57"/>
+      <c r="H24" s="96" t="s">
+        <v>19</v>
+      </c>
+      <c r="I24" s="42"/>
+      <c r="J24" s="56"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="135" t="s">
-        <v>80</v>
-      </c>
-      <c r="B25" s="109"/>
-      <c r="C25" s="110"/>
+      <c r="A25" s="92" t="s">
+        <v>73</v>
+      </c>
+      <c r="B25" s="93"/>
+      <c r="C25" s="94"/>
       <c r="D25" s="16"/>
       <c r="E25" s="16" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="F25" s="17" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="H25" s="76" t="s">
-        <v>87</v>
-      </c>
-      <c r="I25" s="77"/>
-      <c r="J25" s="78"/>
+        <v>77</v>
+      </c>
+      <c r="H25" s="55" t="s">
+        <v>80</v>
+      </c>
+      <c r="I25" s="58"/>
+      <c r="J25" s="59"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A26" s="136"/>
-      <c r="B26" s="137"/>
-      <c r="C26" s="138"/>
-      <c r="D26" s="139"/>
-      <c r="E26" s="139"/>
-      <c r="F26" s="140"/>
-      <c r="G26" s="140"/>
-      <c r="H26" s="72"/>
-      <c r="I26" s="141"/>
-      <c r="J26" s="142"/>
+      <c r="A26" s="99"/>
+      <c r="B26" s="100"/>
+      <c r="C26" s="101"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="40"/>
+      <c r="G26" s="40"/>
+      <c r="H26" s="49"/>
+      <c r="I26" s="97"/>
+      <c r="J26" s="98"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="28" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8894,30 +8841,6 @@
     <row r="997" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A18:J18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A22:J22"/>
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="D15:H15"/>
@@ -8929,6 +8852,30 @@
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="I2:I4"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8948,182 +8895,184 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="61" t="s">
+      <c r="A1" s="62" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="79" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="103"/>
+      <c r="I1" s="103"/>
+      <c r="J1" s="80"/>
+      <c r="K1" s="79" t="s">
+        <v>6</v>
+      </c>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="80"/>
+      <c r="O1" s="79" t="s">
+        <v>7</v>
+      </c>
+      <c r="P1" s="80"/>
+      <c r="Q1" s="79" t="s">
+        <v>8</v>
+      </c>
+      <c r="R1" s="80"/>
+      <c r="S1" s="79" t="s">
+        <v>9</v>
+      </c>
+      <c r="T1" s="133"/>
+    </row>
+    <row r="2" spans="1:26" ht="18" customHeight="1">
+      <c r="A2" s="65"/>
+      <c r="B2" s="45"/>
+      <c r="C2" s="45"/>
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="81" t="s">
+        <v>67</v>
+      </c>
+      <c r="H2" s="106"/>
+      <c r="I2" s="106"/>
+      <c r="J2" s="82"/>
+      <c r="K2" s="81"/>
+      <c r="L2" s="106"/>
+      <c r="M2" s="106"/>
+      <c r="N2" s="82"/>
+      <c r="O2" s="81"/>
+      <c r="P2" s="82"/>
+      <c r="Q2" s="81"/>
+      <c r="R2" s="82"/>
+      <c r="S2" s="81"/>
+      <c r="T2" s="138"/>
+    </row>
+    <row r="3" spans="1:26" ht="18" customHeight="1">
+      <c r="A3" s="65"/>
+      <c r="B3" s="45"/>
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="45"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="83"/>
+      <c r="H3" s="45"/>
+      <c r="I3" s="45"/>
+      <c r="J3" s="66"/>
+      <c r="K3" s="83"/>
+      <c r="L3" s="45"/>
+      <c r="M3" s="45"/>
+      <c r="N3" s="66"/>
+      <c r="O3" s="83"/>
+      <c r="P3" s="66"/>
+      <c r="Q3" s="83"/>
+      <c r="R3" s="66"/>
+      <c r="S3" s="83"/>
+      <c r="T3" s="139"/>
+    </row>
+    <row r="4" spans="1:26" ht="18" customHeight="1">
+      <c r="A4" s="88"/>
+      <c r="B4" s="89"/>
+      <c r="C4" s="89"/>
+      <c r="D4" s="89"/>
+      <c r="E4" s="89"/>
+      <c r="F4" s="90"/>
+      <c r="G4" s="91"/>
+      <c r="H4" s="89"/>
+      <c r="I4" s="89"/>
+      <c r="J4" s="90"/>
+      <c r="K4" s="91"/>
+      <c r="L4" s="89"/>
+      <c r="M4" s="89"/>
+      <c r="N4" s="90"/>
+      <c r="O4" s="91"/>
+      <c r="P4" s="90"/>
+      <c r="Q4" s="91"/>
+      <c r="R4" s="90"/>
+      <c r="S4" s="91"/>
+      <c r="T4" s="140"/>
+    </row>
+    <row r="5" spans="1:26" ht="18" customHeight="1">
+      <c r="A5" s="131" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="62"/>
-      <c r="C1" s="62"/>
-      <c r="D1" s="62"/>
-      <c r="E1" s="62"/>
-      <c r="F1" s="63"/>
-      <c r="G1" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="88"/>
-      <c r="I1" s="88"/>
-      <c r="J1" s="44"/>
-      <c r="K1" s="43" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="88"/>
-      <c r="M1" s="88"/>
-      <c r="N1" s="44"/>
-      <c r="O1" s="43" t="s">
-        <v>8</v>
-      </c>
-      <c r="P1" s="44"/>
-      <c r="Q1" s="43" t="s">
-        <v>9</v>
-      </c>
-      <c r="R1" s="44"/>
-      <c r="S1" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="T1" s="92"/>
-    </row>
-    <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="64"/>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="45"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="45"/>
-      <c r="L2" s="94"/>
-      <c r="M2" s="94"/>
-      <c r="N2" s="46"/>
-      <c r="O2" s="45"/>
-      <c r="P2" s="46"/>
-      <c r="Q2" s="45"/>
-      <c r="R2" s="46"/>
-      <c r="S2" s="45"/>
-      <c r="T2" s="95"/>
-    </row>
-    <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="64"/>
-      <c r="B3" s="39"/>
-      <c r="C3" s="39"/>
-      <c r="D3" s="39"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="48"/>
-      <c r="G3" s="47"/>
-      <c r="H3" s="39"/>
-      <c r="I3" s="39"/>
-      <c r="J3" s="48"/>
-      <c r="K3" s="47"/>
-      <c r="L3" s="39"/>
-      <c r="M3" s="39"/>
-      <c r="N3" s="48"/>
-      <c r="O3" s="47"/>
-      <c r="P3" s="48"/>
-      <c r="Q3" s="47"/>
-      <c r="R3" s="48"/>
-      <c r="S3" s="47"/>
-      <c r="T3" s="96"/>
-    </row>
-    <row r="4" spans="1:26" ht="18" customHeight="1">
-      <c r="A4" s="82"/>
-      <c r="B4" s="83"/>
-      <c r="C4" s="83"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="83"/>
-      <c r="I4" s="83"/>
-      <c r="J4" s="84"/>
-      <c r="K4" s="85"/>
-      <c r="L4" s="83"/>
-      <c r="M4" s="83"/>
-      <c r="N4" s="84"/>
-      <c r="O4" s="85"/>
-      <c r="P4" s="84"/>
-      <c r="Q4" s="85"/>
-      <c r="R4" s="84"/>
-      <c r="S4" s="85"/>
-      <c r="T4" s="102"/>
-    </row>
-    <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="87" t="s">
+      <c r="B5" s="103"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="80"/>
+      <c r="G5" s="132" t="s">
         <v>35</v>
       </c>
-      <c r="B5" s="88"/>
-      <c r="C5" s="88"/>
-      <c r="D5" s="88"/>
-      <c r="E5" s="88"/>
-      <c r="F5" s="44"/>
-      <c r="G5" s="103" t="s">
+      <c r="H5" s="103"/>
+      <c r="I5" s="103"/>
+      <c r="J5" s="103"/>
+      <c r="K5" s="103"/>
+      <c r="L5" s="103"/>
+      <c r="M5" s="103"/>
+      <c r="N5" s="103"/>
+      <c r="O5" s="103"/>
+      <c r="P5" s="103"/>
+      <c r="Q5" s="103"/>
+      <c r="R5" s="103"/>
+      <c r="S5" s="103"/>
+      <c r="T5" s="133"/>
+    </row>
+    <row r="6" spans="1:26" ht="18" customHeight="1">
+      <c r="A6" s="134" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="88"/>
-      <c r="I5" s="88"/>
-      <c r="J5" s="88"/>
-      <c r="K5" s="88"/>
-      <c r="L5" s="88"/>
-      <c r="M5" s="88"/>
-      <c r="N5" s="88"/>
-      <c r="O5" s="88"/>
-      <c r="P5" s="88"/>
-      <c r="Q5" s="88"/>
-      <c r="R5" s="88"/>
-      <c r="S5" s="88"/>
-      <c r="T5" s="92"/>
-    </row>
-    <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="86" t="s">
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="55" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="42"/>
+      <c r="K6" s="42"/>
+      <c r="L6" s="42"/>
+      <c r="M6" s="42"/>
+      <c r="N6" s="42"/>
+      <c r="O6" s="42"/>
+      <c r="P6" s="42"/>
+      <c r="Q6" s="42"/>
+      <c r="R6" s="42"/>
+      <c r="S6" s="42"/>
+      <c r="T6" s="135"/>
+    </row>
+    <row r="7" spans="1:26" ht="18" customHeight="1">
+      <c r="A7" s="134" t="s">
         <v>37</v>
       </c>
-      <c r="B6" s="36"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="76" t="s">
-        <v>21</v>
-      </c>
-      <c r="H6" s="36"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="36"/>
-      <c r="K6" s="36"/>
-      <c r="L6" s="36"/>
-      <c r="M6" s="36"/>
-      <c r="N6" s="36"/>
-      <c r="O6" s="36"/>
-      <c r="P6" s="36"/>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="36"/>
-      <c r="S6" s="36"/>
-      <c r="T6" s="93"/>
-    </row>
-    <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="86" t="s">
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="42"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="43"/>
+      <c r="G7" s="55" t="s">
         <v>38</v>
       </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="76" t="s">
-        <v>39</v>
-      </c>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="36"/>
-      <c r="K7" s="36"/>
-      <c r="L7" s="36"/>
-      <c r="M7" s="36"/>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36"/>
-      <c r="P7" s="36"/>
-      <c r="Q7" s="36"/>
-      <c r="R7" s="36"/>
-      <c r="S7" s="36"/>
-      <c r="T7" s="93"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="42"/>
+      <c r="K7" s="42"/>
+      <c r="L7" s="42"/>
+      <c r="M7" s="42"/>
+      <c r="N7" s="42"/>
+      <c r="O7" s="42"/>
+      <c r="P7" s="42"/>
+      <c r="Q7" s="42"/>
+      <c r="R7" s="42"/>
+      <c r="S7" s="42"/>
+      <c r="T7" s="135"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -9151,11 +9100,11 @@
       <c r="A9" s="18"/>
       <c r="B9" s="19"/>
       <c r="C9" s="20" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D9" s="21"/>
       <c r="E9" s="21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F9" s="21"/>
       <c r="G9" s="22"/>
@@ -9185,7 +9134,7 @@
       <c r="C10" s="24"/>
       <c r="D10" s="19"/>
       <c r="E10" s="19" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F10" s="19"/>
       <c r="G10" s="25"/>
@@ -9215,7 +9164,7 @@
       <c r="C11" s="24"/>
       <c r="D11" s="19"/>
       <c r="E11" s="19" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="F11" s="19"/>
       <c r="G11" s="25"/>
@@ -9245,7 +9194,7 @@
       <c r="C12" s="24"/>
       <c r="D12" s="19"/>
       <c r="E12" s="19" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F12" s="19"/>
       <c r="G12" s="25"/>
@@ -9275,7 +9224,7 @@
       <c r="C13" s="26"/>
       <c r="D13" s="27"/>
       <c r="E13" s="27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F13" s="27"/>
       <c r="G13" s="28"/>
@@ -9322,79 +9271,79 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="86" t="s">
+      <c r="A15" s="134" t="s">
+        <v>45</v>
+      </c>
+      <c r="B15" s="43"/>
+      <c r="C15" s="137" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="43"/>
+      <c r="E15" s="96" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="37"/>
-      <c r="C15" s="106" t="s">
-        <v>40</v>
-      </c>
-      <c r="D15" s="37"/>
-      <c r="E15" s="97" t="s">
+      <c r="F15" s="43"/>
+      <c r="G15" s="96" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="37"/>
-      <c r="G15" s="97" t="s">
+      <c r="H15" s="42"/>
+      <c r="I15" s="43"/>
+      <c r="J15" s="96" t="s">
         <v>48</v>
       </c>
-      <c r="H15" s="36"/>
-      <c r="I15" s="37"/>
-      <c r="J15" s="97" t="s">
+      <c r="K15" s="43"/>
+      <c r="L15" s="96" t="s">
         <v>49</v>
       </c>
-      <c r="K15" s="37"/>
-      <c r="L15" s="97" t="s">
+      <c r="M15" s="42"/>
+      <c r="N15" s="43"/>
+      <c r="O15" s="96" t="s">
         <v>50</v>
       </c>
-      <c r="M15" s="36"/>
-      <c r="N15" s="37"/>
-      <c r="O15" s="97" t="s">
+      <c r="P15" s="42"/>
+      <c r="Q15" s="43"/>
+      <c r="R15" s="15" t="s">
         <v>51</v>
       </c>
-      <c r="P15" s="36"/>
-      <c r="Q15" s="37"/>
-      <c r="R15" s="15" t="s">
+      <c r="S15" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="S15" s="15" t="s">
+      <c r="T15" s="29" t="s">
         <v>53</v>
       </c>
-      <c r="T15" s="29" t="s">
+    </row>
+    <row r="16" spans="1:26" ht="48" customHeight="1">
+      <c r="A16" s="123">
+        <v>1</v>
+      </c>
+      <c r="B16" s="43"/>
+      <c r="C16" s="124" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="104">
-        <v>1</v>
-      </c>
-      <c r="B16" s="37"/>
-      <c r="C16" s="105" t="s">
+      <c r="D16" s="43"/>
+      <c r="E16" s="124" t="s">
         <v>55</v>
       </c>
-      <c r="D16" s="37"/>
-      <c r="E16" s="105" t="s">
+      <c r="F16" s="43"/>
+      <c r="G16" s="136" t="s">
         <v>56</v>
       </c>
-      <c r="F16" s="37"/>
-      <c r="G16" s="98" t="s">
+      <c r="H16" s="42"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="136" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="36"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="98" t="s">
+      <c r="K16" s="43"/>
+      <c r="L16" s="128" t="s">
         <v>58</v>
       </c>
-      <c r="K16" s="37"/>
-      <c r="L16" s="100" t="s">
+      <c r="M16" s="42"/>
+      <c r="N16" s="43"/>
+      <c r="O16" s="128" t="s">
         <v>59</v>
       </c>
-      <c r="M16" s="36"/>
-      <c r="N16" s="37"/>
-      <c r="O16" s="100" t="s">
-        <v>60</v>
-      </c>
-      <c r="P16" s="36"/>
-      <c r="Q16" s="37"/>
+      <c r="P16" s="42"/>
+      <c r="Q16" s="43"/>
       <c r="R16" s="30"/>
       <c r="S16" s="30"/>
       <c r="T16" s="31"/>
@@ -9406,37 +9355,37 @@
       <c r="Z16" s="32"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="104">
+      <c r="A17" s="123">
         <v>2</v>
       </c>
-      <c r="B17" s="37"/>
-      <c r="C17" s="105" t="s">
+      <c r="B17" s="43"/>
+      <c r="C17" s="124" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="43"/>
+      <c r="E17" s="124" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="37"/>
-      <c r="E17" s="105" t="s">
+      <c r="F17" s="43"/>
+      <c r="G17" s="136" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="37"/>
-      <c r="G17" s="98" t="s">
+      <c r="H17" s="42"/>
+      <c r="I17" s="43"/>
+      <c r="J17" s="136" t="s">
         <v>63</v>
       </c>
-      <c r="H17" s="36"/>
-      <c r="I17" s="37"/>
-      <c r="J17" s="98" t="s">
+      <c r="K17" s="43"/>
+      <c r="L17" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="K17" s="37"/>
-      <c r="L17" s="100" t="s">
+      <c r="M17" s="42"/>
+      <c r="N17" s="43"/>
+      <c r="O17" s="128" t="s">
         <v>65</v>
       </c>
-      <c r="M17" s="36"/>
-      <c r="N17" s="37"/>
-      <c r="O17" s="100" t="s">
-        <v>66</v>
-      </c>
-      <c r="P17" s="36"/>
-      <c r="Q17" s="37"/>
+      <c r="P17" s="42"/>
+      <c r="Q17" s="43"/>
       <c r="R17" s="30"/>
       <c r="S17" s="30"/>
       <c r="T17" s="31"/>
@@ -9448,25 +9397,25 @@
       <c r="Z17" s="32"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="104"/>
-      <c r="B18" s="37"/>
-      <c r="C18" s="105"/>
-      <c r="D18" s="37"/>
-      <c r="E18" s="105"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="98" t="s">
-        <v>76</v>
-      </c>
-      <c r="H18" s="36"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="98"/>
-      <c r="K18" s="37"/>
-      <c r="L18" s="100"/>
-      <c r="M18" s="36"/>
-      <c r="N18" s="37"/>
-      <c r="O18" s="100"/>
-      <c r="P18" s="36"/>
-      <c r="Q18" s="37"/>
+      <c r="A18" s="123"/>
+      <c r="B18" s="43"/>
+      <c r="C18" s="124"/>
+      <c r="D18" s="43"/>
+      <c r="E18" s="124"/>
+      <c r="F18" s="43"/>
+      <c r="G18" s="136" t="s">
+        <v>69</v>
+      </c>
+      <c r="H18" s="42"/>
+      <c r="I18" s="43"/>
+      <c r="J18" s="136"/>
+      <c r="K18" s="43"/>
+      <c r="L18" s="128"/>
+      <c r="M18" s="42"/>
+      <c r="N18" s="43"/>
+      <c r="O18" s="128"/>
+      <c r="P18" s="42"/>
+      <c r="Q18" s="43"/>
       <c r="R18" s="30"/>
       <c r="S18" s="30"/>
       <c r="T18" s="31"/>
@@ -9478,25 +9427,25 @@
       <c r="Z18" s="32"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="104"/>
-      <c r="B19" s="37"/>
-      <c r="C19" s="105"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="105"/>
-      <c r="F19" s="37"/>
-      <c r="G19" s="98" t="s">
-        <v>77</v>
-      </c>
-      <c r="H19" s="36"/>
-      <c r="I19" s="37"/>
-      <c r="J19" s="98"/>
-      <c r="K19" s="37"/>
-      <c r="L19" s="100"/>
-      <c r="M19" s="36"/>
-      <c r="N19" s="37"/>
-      <c r="O19" s="100"/>
-      <c r="P19" s="36"/>
-      <c r="Q19" s="37"/>
+      <c r="A19" s="123"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="124"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="124"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="136" t="s">
+        <v>70</v>
+      </c>
+      <c r="H19" s="42"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="136"/>
+      <c r="K19" s="43"/>
+      <c r="L19" s="128"/>
+      <c r="M19" s="42"/>
+      <c r="N19" s="43"/>
+      <c r="O19" s="128"/>
+      <c r="P19" s="42"/>
+      <c r="Q19" s="43"/>
       <c r="R19" s="30"/>
       <c r="S19" s="30"/>
       <c r="T19" s="31"/>
@@ -9508,23 +9457,23 @@
       <c r="Z19" s="32"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="104"/>
-      <c r="B20" s="37"/>
-      <c r="C20" s="105"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="105"/>
-      <c r="F20" s="37"/>
-      <c r="G20" s="98"/>
-      <c r="H20" s="36"/>
-      <c r="I20" s="37"/>
-      <c r="J20" s="98"/>
-      <c r="K20" s="37"/>
-      <c r="L20" s="100"/>
-      <c r="M20" s="36"/>
-      <c r="N20" s="37"/>
-      <c r="O20" s="100"/>
-      <c r="P20" s="36"/>
-      <c r="Q20" s="37"/>
+      <c r="A20" s="123"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="124"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="124"/>
+      <c r="F20" s="43"/>
+      <c r="G20" s="136"/>
+      <c r="H20" s="42"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="136"/>
+      <c r="K20" s="43"/>
+      <c r="L20" s="128"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="43"/>
+      <c r="O20" s="128"/>
+      <c r="P20" s="42"/>
+      <c r="Q20" s="43"/>
       <c r="R20" s="30"/>
       <c r="S20" s="30"/>
       <c r="T20" s="31"/>
@@ -9536,23 +9485,23 @@
       <c r="Z20" s="32"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="104"/>
-      <c r="B21" s="37"/>
-      <c r="C21" s="105"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="105"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="98"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="37"/>
-      <c r="J21" s="98"/>
-      <c r="K21" s="37"/>
-      <c r="L21" s="100"/>
-      <c r="M21" s="36"/>
-      <c r="N21" s="37"/>
-      <c r="O21" s="100"/>
-      <c r="P21" s="36"/>
-      <c r="Q21" s="37"/>
+      <c r="A21" s="123"/>
+      <c r="B21" s="43"/>
+      <c r="C21" s="124"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="124"/>
+      <c r="F21" s="43"/>
+      <c r="G21" s="136"/>
+      <c r="H21" s="42"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="136"/>
+      <c r="K21" s="43"/>
+      <c r="L21" s="128"/>
+      <c r="M21" s="42"/>
+      <c r="N21" s="43"/>
+      <c r="O21" s="128"/>
+      <c r="P21" s="42"/>
+      <c r="Q21" s="43"/>
       <c r="R21" s="30"/>
       <c r="S21" s="30"/>
       <c r="T21" s="31"/>
@@ -9564,23 +9513,23 @@
       <c r="Z21" s="32"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="104"/>
-      <c r="B22" s="37"/>
-      <c r="C22" s="105"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="105"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="98"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="98"/>
-      <c r="K22" s="37"/>
-      <c r="L22" s="100"/>
-      <c r="M22" s="36"/>
-      <c r="N22" s="37"/>
-      <c r="O22" s="100"/>
-      <c r="P22" s="36"/>
-      <c r="Q22" s="37"/>
+      <c r="A22" s="123"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="124"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="124"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="136"/>
+      <c r="H22" s="42"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="136"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="128"/>
+      <c r="M22" s="42"/>
+      <c r="N22" s="43"/>
+      <c r="O22" s="128"/>
+      <c r="P22" s="42"/>
+      <c r="Q22" s="43"/>
       <c r="R22" s="30"/>
       <c r="S22" s="30"/>
       <c r="T22" s="31"/>
@@ -9592,23 +9541,23 @@
       <c r="Z22" s="32"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="104"/>
-      <c r="B23" s="37"/>
-      <c r="C23" s="105"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="105"/>
-      <c r="F23" s="37"/>
-      <c r="G23" s="98"/>
-      <c r="H23" s="36"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="98"/>
-      <c r="K23" s="37"/>
-      <c r="L23" s="100"/>
-      <c r="M23" s="36"/>
-      <c r="N23" s="37"/>
-      <c r="O23" s="100"/>
-      <c r="P23" s="36"/>
-      <c r="Q23" s="37"/>
+      <c r="A23" s="123"/>
+      <c r="B23" s="43"/>
+      <c r="C23" s="124"/>
+      <c r="D23" s="43"/>
+      <c r="E23" s="124"/>
+      <c r="F23" s="43"/>
+      <c r="G23" s="136"/>
+      <c r="H23" s="42"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="136"/>
+      <c r="K23" s="43"/>
+      <c r="L23" s="128"/>
+      <c r="M23" s="42"/>
+      <c r="N23" s="43"/>
+      <c r="O23" s="128"/>
+      <c r="P23" s="42"/>
+      <c r="Q23" s="43"/>
       <c r="R23" s="30"/>
       <c r="S23" s="30"/>
       <c r="T23" s="31"/>
@@ -9620,23 +9569,23 @@
       <c r="Z23" s="32"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="104"/>
-      <c r="B24" s="37"/>
-      <c r="C24" s="105"/>
-      <c r="D24" s="37"/>
-      <c r="E24" s="105"/>
-      <c r="F24" s="37"/>
-      <c r="G24" s="98"/>
-      <c r="H24" s="36"/>
-      <c r="I24" s="37"/>
-      <c r="J24" s="98"/>
-      <c r="K24" s="37"/>
-      <c r="L24" s="100"/>
-      <c r="M24" s="36"/>
-      <c r="N24" s="37"/>
-      <c r="O24" s="100"/>
-      <c r="P24" s="36"/>
-      <c r="Q24" s="37"/>
+      <c r="A24" s="123"/>
+      <c r="B24" s="43"/>
+      <c r="C24" s="124"/>
+      <c r="D24" s="43"/>
+      <c r="E24" s="124"/>
+      <c r="F24" s="43"/>
+      <c r="G24" s="136"/>
+      <c r="H24" s="42"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="136"/>
+      <c r="K24" s="43"/>
+      <c r="L24" s="128"/>
+      <c r="M24" s="42"/>
+      <c r="N24" s="43"/>
+      <c r="O24" s="128"/>
+      <c r="P24" s="42"/>
+      <c r="Q24" s="43"/>
       <c r="R24" s="30"/>
       <c r="S24" s="30"/>
       <c r="T24" s="31"/>
@@ -9648,23 +9597,23 @@
       <c r="Z24" s="32"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="104"/>
-      <c r="B25" s="37"/>
-      <c r="C25" s="105"/>
-      <c r="D25" s="37"/>
-      <c r="E25" s="105"/>
-      <c r="F25" s="37"/>
-      <c r="G25" s="98"/>
-      <c r="H25" s="36"/>
-      <c r="I25" s="37"/>
-      <c r="J25" s="98"/>
-      <c r="K25" s="37"/>
-      <c r="L25" s="100"/>
-      <c r="M25" s="36"/>
-      <c r="N25" s="37"/>
-      <c r="O25" s="100"/>
-      <c r="P25" s="36"/>
-      <c r="Q25" s="37"/>
+      <c r="A25" s="123"/>
+      <c r="B25" s="43"/>
+      <c r="C25" s="124"/>
+      <c r="D25" s="43"/>
+      <c r="E25" s="124"/>
+      <c r="F25" s="43"/>
+      <c r="G25" s="136"/>
+      <c r="H25" s="42"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="136"/>
+      <c r="K25" s="43"/>
+      <c r="L25" s="128"/>
+      <c r="M25" s="42"/>
+      <c r="N25" s="43"/>
+      <c r="O25" s="128"/>
+      <c r="P25" s="42"/>
+      <c r="Q25" s="43"/>
       <c r="R25" s="30"/>
       <c r="S25" s="30"/>
       <c r="T25" s="31"/>
@@ -9676,23 +9625,23 @@
       <c r="Z25" s="32"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="104"/>
-      <c r="B26" s="37"/>
-      <c r="C26" s="105"/>
-      <c r="D26" s="37"/>
-      <c r="E26" s="105"/>
-      <c r="F26" s="37"/>
-      <c r="G26" s="98"/>
-      <c r="H26" s="36"/>
-      <c r="I26" s="37"/>
-      <c r="J26" s="98"/>
-      <c r="K26" s="37"/>
-      <c r="L26" s="100"/>
-      <c r="M26" s="36"/>
-      <c r="N26" s="37"/>
-      <c r="O26" s="100"/>
-      <c r="P26" s="36"/>
-      <c r="Q26" s="37"/>
+      <c r="A26" s="123"/>
+      <c r="B26" s="43"/>
+      <c r="C26" s="124"/>
+      <c r="D26" s="43"/>
+      <c r="E26" s="124"/>
+      <c r="F26" s="43"/>
+      <c r="G26" s="136"/>
+      <c r="H26" s="42"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="136"/>
+      <c r="K26" s="43"/>
+      <c r="L26" s="128"/>
+      <c r="M26" s="42"/>
+      <c r="N26" s="43"/>
+      <c r="O26" s="128"/>
+      <c r="P26" s="42"/>
+      <c r="Q26" s="43"/>
       <c r="R26" s="30"/>
       <c r="S26" s="30"/>
       <c r="T26" s="31"/>
@@ -9704,23 +9653,23 @@
       <c r="Z26" s="32"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="104"/>
-      <c r="B27" s="37"/>
-      <c r="C27" s="105"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="105"/>
-      <c r="F27" s="37"/>
-      <c r="G27" s="98"/>
-      <c r="H27" s="36"/>
-      <c r="I27" s="37"/>
-      <c r="J27" s="98"/>
-      <c r="K27" s="37"/>
-      <c r="L27" s="100"/>
-      <c r="M27" s="36"/>
-      <c r="N27" s="37"/>
-      <c r="O27" s="100"/>
-      <c r="P27" s="36"/>
-      <c r="Q27" s="37"/>
+      <c r="A27" s="123"/>
+      <c r="B27" s="43"/>
+      <c r="C27" s="124"/>
+      <c r="D27" s="43"/>
+      <c r="E27" s="124"/>
+      <c r="F27" s="43"/>
+      <c r="G27" s="136"/>
+      <c r="H27" s="42"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="136"/>
+      <c r="K27" s="43"/>
+      <c r="L27" s="128"/>
+      <c r="M27" s="42"/>
+      <c r="N27" s="43"/>
+      <c r="O27" s="128"/>
+      <c r="P27" s="42"/>
+      <c r="Q27" s="43"/>
       <c r="R27" s="30"/>
       <c r="S27" s="30"/>
       <c r="T27" s="31"/>
@@ -9732,23 +9681,23 @@
       <c r="Z27" s="32"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="104"/>
-      <c r="B28" s="37"/>
-      <c r="C28" s="105"/>
-      <c r="D28" s="37"/>
-      <c r="E28" s="105"/>
-      <c r="F28" s="37"/>
-      <c r="G28" s="98"/>
-      <c r="H28" s="36"/>
-      <c r="I28" s="37"/>
-      <c r="J28" s="98"/>
-      <c r="K28" s="37"/>
-      <c r="L28" s="100"/>
-      <c r="M28" s="36"/>
-      <c r="N28" s="37"/>
-      <c r="O28" s="100"/>
-      <c r="P28" s="36"/>
-      <c r="Q28" s="37"/>
+      <c r="A28" s="123"/>
+      <c r="B28" s="43"/>
+      <c r="C28" s="124"/>
+      <c r="D28" s="43"/>
+      <c r="E28" s="124"/>
+      <c r="F28" s="43"/>
+      <c r="G28" s="136"/>
+      <c r="H28" s="42"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="136"/>
+      <c r="K28" s="43"/>
+      <c r="L28" s="128"/>
+      <c r="M28" s="42"/>
+      <c r="N28" s="43"/>
+      <c r="O28" s="128"/>
+      <c r="P28" s="42"/>
+      <c r="Q28" s="43"/>
       <c r="R28" s="30"/>
       <c r="S28" s="30"/>
       <c r="T28" s="31"/>
@@ -9760,23 +9709,23 @@
       <c r="Z28" s="32"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="104"/>
-      <c r="B29" s="37"/>
-      <c r="C29" s="105"/>
-      <c r="D29" s="37"/>
-      <c r="E29" s="105"/>
-      <c r="F29" s="37"/>
-      <c r="G29" s="98"/>
-      <c r="H29" s="36"/>
-      <c r="I29" s="37"/>
-      <c r="J29" s="98"/>
-      <c r="K29" s="37"/>
-      <c r="L29" s="100"/>
-      <c r="M29" s="36"/>
-      <c r="N29" s="37"/>
-      <c r="O29" s="100"/>
-      <c r="P29" s="36"/>
-      <c r="Q29" s="37"/>
+      <c r="A29" s="123"/>
+      <c r="B29" s="43"/>
+      <c r="C29" s="124"/>
+      <c r="D29" s="43"/>
+      <c r="E29" s="124"/>
+      <c r="F29" s="43"/>
+      <c r="G29" s="136"/>
+      <c r="H29" s="42"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="136"/>
+      <c r="K29" s="43"/>
+      <c r="L29" s="128"/>
+      <c r="M29" s="42"/>
+      <c r="N29" s="43"/>
+      <c r="O29" s="128"/>
+      <c r="P29" s="42"/>
+      <c r="Q29" s="43"/>
       <c r="R29" s="30"/>
       <c r="S29" s="30"/>
       <c r="T29" s="31"/>
@@ -9788,23 +9737,23 @@
       <c r="Z29" s="32"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="104"/>
-      <c r="B30" s="37"/>
-      <c r="C30" s="105"/>
-      <c r="D30" s="37"/>
-      <c r="E30" s="105"/>
-      <c r="F30" s="37"/>
-      <c r="G30" s="98"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="37"/>
-      <c r="J30" s="98"/>
-      <c r="K30" s="37"/>
-      <c r="L30" s="100"/>
-      <c r="M30" s="36"/>
-      <c r="N30" s="37"/>
-      <c r="O30" s="100"/>
-      <c r="P30" s="36"/>
-      <c r="Q30" s="37"/>
+      <c r="A30" s="123"/>
+      <c r="B30" s="43"/>
+      <c r="C30" s="124"/>
+      <c r="D30" s="43"/>
+      <c r="E30" s="124"/>
+      <c r="F30" s="43"/>
+      <c r="G30" s="136"/>
+      <c r="H30" s="42"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="136"/>
+      <c r="K30" s="43"/>
+      <c r="L30" s="128"/>
+      <c r="M30" s="42"/>
+      <c r="N30" s="43"/>
+      <c r="O30" s="128"/>
+      <c r="P30" s="42"/>
+      <c r="Q30" s="43"/>
       <c r="R30" s="30"/>
       <c r="S30" s="30"/>
       <c r="T30" s="31"/>
@@ -9816,23 +9765,23 @@
       <c r="Z30" s="32"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="107"/>
-      <c r="B31" s="90"/>
-      <c r="C31" s="108"/>
-      <c r="D31" s="90"/>
-      <c r="E31" s="108"/>
-      <c r="F31" s="90"/>
-      <c r="G31" s="99"/>
-      <c r="H31" s="89"/>
-      <c r="I31" s="90"/>
-      <c r="J31" s="99"/>
-      <c r="K31" s="90"/>
-      <c r="L31" s="101"/>
-      <c r="M31" s="89"/>
-      <c r="N31" s="90"/>
-      <c r="O31" s="101"/>
-      <c r="P31" s="89"/>
-      <c r="Q31" s="90"/>
+      <c r="A31" s="125"/>
+      <c r="B31" s="126"/>
+      <c r="C31" s="127"/>
+      <c r="D31" s="126"/>
+      <c r="E31" s="127"/>
+      <c r="F31" s="126"/>
+      <c r="G31" s="141"/>
+      <c r="H31" s="130"/>
+      <c r="I31" s="126"/>
+      <c r="J31" s="141"/>
+      <c r="K31" s="126"/>
+      <c r="L31" s="129"/>
+      <c r="M31" s="130"/>
+      <c r="N31" s="126"/>
+      <c r="O31" s="129"/>
+      <c r="P31" s="130"/>
+      <c r="Q31" s="126"/>
       <c r="R31" s="33"/>
       <c r="S31" s="33"/>
       <c r="T31" s="34"/>
@@ -10830,6 +10779,118 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="G5:T5"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="G6:T6"/>
+    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="G7:T7"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:I20"/>
+    <mergeCell ref="J20:K20"/>
+    <mergeCell ref="L20:N20"/>
+    <mergeCell ref="O20:Q20"/>
+    <mergeCell ref="L15:N15"/>
+    <mergeCell ref="O15:Q15"/>
+    <mergeCell ref="L16:N16"/>
+    <mergeCell ref="O16:Q16"/>
+    <mergeCell ref="L17:N17"/>
+    <mergeCell ref="O17:Q17"/>
+    <mergeCell ref="O18:Q18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="E30:F30"/>
@@ -10854,118 +10915,6 @@
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="E28:F28"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="G5:T5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="G6:T6"/>
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="G7:T7"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:I20"/>
-    <mergeCell ref="J20:K20"/>
-    <mergeCell ref="L20:N20"/>
-    <mergeCell ref="O20:Q20"/>
-    <mergeCell ref="L15:N15"/>
-    <mergeCell ref="O15:Q15"/>
-    <mergeCell ref="L16:N16"/>
-    <mergeCell ref="O16:Q16"/>
-    <mergeCell ref="L17:N17"/>
-    <mergeCell ref="O17:Q17"/>
-    <mergeCell ref="O18:Q18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/詳細設計図/メニュー画面_詳細設計図.xlsx
+++ b/詳細設計図/メニュー画面_詳細設計図.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\S-04\Documents\プロジェクト演習\詳細設計図\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{249644D2-D8BD-4876-A667-28D01F274C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CD16DD2-F64A-49D7-AB74-54B7A60D9BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -326,15 +326,7 @@
     <phoneticPr fontId="8"/>
   </si>
   <si>
-    <t>task-add.jsp</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
     <t>POST</t>
-    <phoneticPr fontId="8"/>
-  </si>
-  <si>
-    <t>logout.jsp</t>
     <phoneticPr fontId="8"/>
   </si>
   <si>
@@ -399,6 +391,14 @@
     <rPh sb="53" eb="55">
       <t>センイ</t>
     </rPh>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>LogoutServlet</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>TaskAddTrasitionAgoServlet</t>
     <phoneticPr fontId="8"/>
   </si>
 </sst>
@@ -1655,114 +1655,114 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1784,27 +1784,90 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1814,68 +1877,47 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="77" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="78" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="79" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="73" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="80" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="81" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="68" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="82" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="83" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="74" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="75" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="70" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="71" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="76" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1883,56 +1925,14 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3378,19 +3378,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="79" t="s">
+      <c r="B1" s="68"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="80"/>
-      <c r="F1" s="79" t="s">
+      <c r="E1" s="50"/>
+      <c r="F1" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="80"/>
+      <c r="G1" s="50"/>
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
@@ -3402,86 +3402,86 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="65"/>
+      <c r="A2" s="70"/>
       <c r="B2" s="45"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="81" t="s">
+      <c r="C2" s="54"/>
+      <c r="D2" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="82"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="84">
+      <c r="E2" s="52"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="55">
         <v>45705</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="77"/>
+      <c r="J2" s="58"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="65"/>
+      <c r="A3" s="70"/>
       <c r="B3" s="45"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="78"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
-      <c r="A4" s="65"/>
-      <c r="B4" s="67"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="78"/>
+      <c r="A4" s="70"/>
+      <c r="B4" s="71"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="59"/>
     </row>
     <row r="5" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A5" s="68" t="s">
+      <c r="A5" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="53"/>
-      <c r="C5" s="69"/>
-      <c r="D5" s="52" t="s">
-        <v>85</v>
-      </c>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="54"/>
+      <c r="B5" s="73"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="80" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="81"/>
     </row>
     <row r="6" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A6" s="70" t="s">
+      <c r="A6" s="61" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="42"/>
       <c r="C6" s="43"/>
-      <c r="D6" s="55" t="s">
-        <v>86</v>
+      <c r="D6" s="82" t="s">
+        <v>84</v>
       </c>
       <c r="E6" s="42"/>
       <c r="F6" s="42"/>
       <c r="G6" s="42"/>
       <c r="H6" s="42"/>
       <c r="I6" s="42"/>
-      <c r="J6" s="56"/>
+      <c r="J6" s="63"/>
     </row>
     <row r="7" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A7" s="70" t="s">
+      <c r="A7" s="61" t="s">
         <v>12</v>
       </c>
       <c r="B7" s="42"/>
       <c r="C7" s="43"/>
-      <c r="D7" s="55" t="s">
+      <c r="D7" s="82" t="s">
         <v>66</v>
       </c>
       <c r="E7" s="42"/>
@@ -3489,99 +3489,99 @@
       <c r="G7" s="42"/>
       <c r="H7" s="42"/>
       <c r="I7" s="42"/>
-      <c r="J7" s="56"/>
+      <c r="J7" s="63"/>
     </row>
     <row r="8" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A8" s="70" t="s">
+      <c r="A8" s="61" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="42"/>
       <c r="C8" s="43"/>
-      <c r="D8" s="55" t="s">
-        <v>87</v>
+      <c r="D8" s="82" t="s">
+        <v>85</v>
       </c>
       <c r="E8" s="42"/>
       <c r="F8" s="42"/>
       <c r="G8" s="42"/>
       <c r="H8" s="42"/>
       <c r="I8" s="42"/>
-      <c r="J8" s="56"/>
+      <c r="J8" s="63"/>
     </row>
     <row r="9" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A9" s="71" t="s">
+      <c r="A9" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="74" t="s">
+      <c r="B9" s="60" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="43"/>
-      <c r="D9" s="57" t="s">
-        <v>90</v>
-      </c>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58"/>
-      <c r="I9" s="58"/>
-      <c r="J9" s="59"/>
+      <c r="D9" s="62" t="s">
+        <v>88</v>
+      </c>
+      <c r="E9" s="83"/>
+      <c r="F9" s="83"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="83"/>
+      <c r="I9" s="83"/>
+      <c r="J9" s="84"/>
     </row>
     <row r="10" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A10" s="72"/>
-      <c r="B10" s="74" t="s">
+      <c r="A10" s="76"/>
+      <c r="B10" s="60" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="43"/>
-      <c r="D10" s="57"/>
+      <c r="D10" s="62"/>
       <c r="E10" s="42"/>
       <c r="F10" s="42"/>
       <c r="G10" s="42"/>
       <c r="H10" s="42"/>
       <c r="I10" s="42"/>
-      <c r="J10" s="56"/>
+      <c r="J10" s="63"/>
     </row>
     <row r="11" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A11" s="73"/>
-      <c r="B11" s="74" t="s">
+      <c r="A11" s="77"/>
+      <c r="B11" s="60" t="s">
         <v>17</v>
       </c>
       <c r="C11" s="43"/>
-      <c r="D11" s="57"/>
+      <c r="D11" s="62"/>
       <c r="E11" s="42"/>
       <c r="F11" s="42"/>
       <c r="G11" s="42"/>
       <c r="H11" s="42"/>
       <c r="I11" s="42"/>
-      <c r="J11" s="56"/>
+      <c r="J11" s="63"/>
     </row>
     <row r="12" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A12" s="70" t="s">
+      <c r="A12" s="61" t="s">
         <v>18</v>
       </c>
       <c r="B12" s="42"/>
       <c r="C12" s="43"/>
-      <c r="D12" s="57" t="s">
-        <v>88</v>
+      <c r="D12" s="62" t="s">
+        <v>86</v>
       </c>
       <c r="E12" s="42"/>
       <c r="F12" s="42"/>
       <c r="G12" s="42"/>
       <c r="H12" s="42"/>
       <c r="I12" s="42"/>
-      <c r="J12" s="56"/>
+      <c r="J12" s="63"/>
     </row>
     <row r="13" spans="1:10" ht="26.25" customHeight="1">
-      <c r="A13" s="60" t="s">
+      <c r="A13" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="50"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="49"/>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="50"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="50"/>
-      <c r="J13" s="51"/>
+      <c r="B13" s="65"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="78"/>
+      <c r="E13" s="65"/>
+      <c r="F13" s="65"/>
+      <c r="G13" s="65"/>
+      <c r="H13" s="65"/>
+      <c r="I13" s="65"/>
+      <c r="J13" s="79"/>
     </row>
     <row r="14" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="15" spans="1:10" ht="12.75" customHeight="1"/>
@@ -4572,17 +4572,14 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="F1:G1"/>
-    <mergeCell ref="D2:E4"/>
-    <mergeCell ref="F2:G4"/>
-    <mergeCell ref="H2:H4"/>
-    <mergeCell ref="I2:I4"/>
-    <mergeCell ref="J2:J4"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="A12:C12"/>
-    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="D6:J6"/>
+    <mergeCell ref="D7:J7"/>
+    <mergeCell ref="D8:J8"/>
+    <mergeCell ref="D9:J9"/>
+    <mergeCell ref="D10:J10"/>
+    <mergeCell ref="D11:J11"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C4"/>
     <mergeCell ref="A5:C5"/>
@@ -4591,14 +4588,17 @@
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A9:A11"/>
     <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D13:J13"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="D6:J6"/>
-    <mergeCell ref="D7:J7"/>
-    <mergeCell ref="D8:J8"/>
-    <mergeCell ref="D9:J9"/>
-    <mergeCell ref="D10:J10"/>
-    <mergeCell ref="D11:J11"/>
+    <mergeCell ref="I2:I4"/>
+    <mergeCell ref="J2:J4"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="D12:J12"/>
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="F1:G1"/>
+    <mergeCell ref="D2:E4"/>
+    <mergeCell ref="F2:G4"/>
+    <mergeCell ref="H2:H4"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.70833333333333304" right="0.70833333333333304" top="0.74791666666666701" bottom="0.74791666666666701" header="0" footer="0"/>
@@ -4620,16 +4620,16 @@
       <c r="A1" s="87" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="79" t="s">
+      <c r="B1" s="68"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="80"/>
-      <c r="F1" s="79" t="s">
+      <c r="E1" s="50"/>
+      <c r="F1" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="80"/>
+      <c r="G1" s="50"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -4641,28 +4641,28 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="65"/>
+      <c r="A2" s="70"/>
       <c r="B2" s="45"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="77"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="58"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="65"/>
+      <c r="A3" s="70"/>
       <c r="B3" s="45"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="78"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
       <c r="A4" s="88"/>
@@ -6033,16 +6033,16 @@
       <c r="A1" s="87" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="79" t="s">
+      <c r="B1" s="68"/>
+      <c r="C1" s="69"/>
+      <c r="D1" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="80"/>
-      <c r="F1" s="79" t="s">
+      <c r="E1" s="50"/>
+      <c r="F1" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="80"/>
+      <c r="G1" s="50"/>
       <c r="H1" s="4" t="s">
         <v>7</v>
       </c>
@@ -6054,28 +6054,28 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="65"/>
+      <c r="A2" s="70"/>
       <c r="B2" s="45"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="82"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="75"/>
-      <c r="I2" s="75"/>
-      <c r="J2" s="77"/>
+      <c r="C2" s="54"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
+      <c r="J2" s="58"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="65"/>
+      <c r="A3" s="70"/>
       <c r="B3" s="45"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="78"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="59"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1">
       <c r="A4" s="88"/>
@@ -7437,19 +7437,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18" customHeight="1">
-      <c r="A1" s="118" t="s">
+      <c r="A1" s="95" t="s">
         <v>22</v>
       </c>
-      <c r="B1" s="119"/>
-      <c r="C1" s="120"/>
-      <c r="D1" s="122" t="s">
+      <c r="B1" s="96"/>
+      <c r="C1" s="97"/>
+      <c r="D1" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="69"/>
-      <c r="F1" s="122" t="s">
+      <c r="E1" s="74"/>
+      <c r="F1" s="101" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="69"/>
+      <c r="G1" s="74"/>
       <c r="H1" s="35" t="s">
         <v>7</v>
       </c>
@@ -7461,65 +7461,65 @@
       </c>
     </row>
     <row r="2" spans="1:10" ht="18" customHeight="1">
-      <c r="A2" s="108"/>
+      <c r="A2" s="98"/>
       <c r="B2" s="45"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="81" t="s">
+      <c r="C2" s="54"/>
+      <c r="D2" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="E2" s="82"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="82"/>
-      <c r="H2" s="84">
+      <c r="E2" s="52"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="52"/>
+      <c r="H2" s="55">
         <v>45707</v>
       </c>
-      <c r="I2" s="75" t="s">
+      <c r="I2" s="57" t="s">
         <v>68</v>
       </c>
-      <c r="J2" s="116"/>
+      <c r="J2" s="92"/>
     </row>
     <row r="3" spans="1:10" ht="18" customHeight="1">
-      <c r="A3" s="108"/>
+      <c r="A3" s="98"/>
       <c r="B3" s="45"/>
-      <c r="C3" s="66"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="66"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="76"/>
-      <c r="I3" s="76"/>
-      <c r="J3" s="117"/>
+      <c r="C3" s="54"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="54"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+      <c r="J3" s="93"/>
     </row>
     <row r="4" spans="1:10" ht="18" customHeight="1" thickBot="1">
-      <c r="A4" s="108"/>
+      <c r="A4" s="98"/>
       <c r="B4" s="45"/>
-      <c r="C4" s="66"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="66"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="66"/>
-      <c r="H4" s="76"/>
-      <c r="I4" s="76"/>
-      <c r="J4" s="117"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="53"/>
+      <c r="G4" s="54"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="93"/>
     </row>
     <row r="5" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A5" s="121" t="s">
+      <c r="A5" s="99" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="103"/>
-      <c r="C5" s="80"/>
-      <c r="D5" s="102" t="s">
+      <c r="B5" s="100"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="103" t="s">
         <v>81</v>
       </c>
-      <c r="E5" s="103"/>
-      <c r="F5" s="103"/>
-      <c r="G5" s="103"/>
-      <c r="H5" s="103"/>
-      <c r="I5" s="103"/>
+      <c r="E5" s="100"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="100"/>
+      <c r="H5" s="100"/>
+      <c r="I5" s="100"/>
       <c r="J5" s="104"/>
     </row>
     <row r="6" spans="1:10" ht="21" customHeight="1">
-      <c r="A6" s="95" t="s">
+      <c r="A6" s="94" t="s">
         <v>24</v>
       </c>
       <c r="B6" s="42"/>
@@ -7530,7 +7530,7 @@
       <c r="G6" s="42"/>
       <c r="H6" s="42"/>
       <c r="I6" s="42"/>
-      <c r="J6" s="56"/>
+      <c r="J6" s="63"/>
     </row>
     <row r="7" spans="1:10" ht="21" customHeight="1">
       <c r="A7" s="105"/>
@@ -7545,7 +7545,7 @@
       <c r="J7" s="107"/>
     </row>
     <row r="8" spans="1:10" ht="21" customHeight="1">
-      <c r="A8" s="108"/>
+      <c r="A8" s="98"/>
       <c r="B8" s="45"/>
       <c r="C8" s="45"/>
       <c r="D8" s="45"/>
@@ -7554,10 +7554,10 @@
       <c r="G8" s="45"/>
       <c r="H8" s="45"/>
       <c r="I8" s="45"/>
-      <c r="J8" s="109"/>
+      <c r="J8" s="108"/>
     </row>
     <row r="9" spans="1:10" ht="21" customHeight="1">
-      <c r="A9" s="108"/>
+      <c r="A9" s="98"/>
       <c r="B9" s="45"/>
       <c r="C9" s="45"/>
       <c r="D9" s="45"/>
@@ -7566,10 +7566,10 @@
       <c r="G9" s="45"/>
       <c r="H9" s="45"/>
       <c r="I9" s="45"/>
-      <c r="J9" s="109"/>
+      <c r="J9" s="108"/>
     </row>
     <row r="10" spans="1:10" ht="21" customHeight="1">
-      <c r="A10" s="108"/>
+      <c r="A10" s="98"/>
       <c r="B10" s="45"/>
       <c r="C10" s="45"/>
       <c r="D10" s="45"/>
@@ -7578,10 +7578,10 @@
       <c r="G10" s="45"/>
       <c r="H10" s="45"/>
       <c r="I10" s="45"/>
-      <c r="J10" s="109"/>
+      <c r="J10" s="108"/>
     </row>
     <row r="11" spans="1:10" ht="21" customHeight="1">
-      <c r="A11" s="108"/>
+      <c r="A11" s="98"/>
       <c r="B11" s="45"/>
       <c r="C11" s="45"/>
       <c r="D11" s="45"/>
@@ -7590,10 +7590,10 @@
       <c r="G11" s="45"/>
       <c r="H11" s="45"/>
       <c r="I11" s="45"/>
-      <c r="J11" s="109"/>
+      <c r="J11" s="108"/>
     </row>
     <row r="12" spans="1:10" ht="21" customHeight="1">
-      <c r="A12" s="108"/>
+      <c r="A12" s="98"/>
       <c r="B12" s="45"/>
       <c r="C12" s="45"/>
       <c r="D12" s="45"/>
@@ -7602,42 +7602,42 @@
       <c r="G12" s="45"/>
       <c r="H12" s="45"/>
       <c r="I12" s="45"/>
-      <c r="J12" s="109"/>
+      <c r="J12" s="108"/>
     </row>
     <row r="13" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A13" s="110"/>
-      <c r="B13" s="111"/>
-      <c r="C13" s="111"/>
-      <c r="D13" s="111"/>
-      <c r="E13" s="111"/>
-      <c r="F13" s="111"/>
-      <c r="G13" s="111"/>
-      <c r="H13" s="111"/>
-      <c r="I13" s="111"/>
-      <c r="J13" s="112"/>
+      <c r="A13" s="109"/>
+      <c r="B13" s="110"/>
+      <c r="C13" s="110"/>
+      <c r="D13" s="110"/>
+      <c r="E13" s="110"/>
+      <c r="F13" s="110"/>
+      <c r="G13" s="110"/>
+      <c r="H13" s="110"/>
+      <c r="I13" s="110"/>
+      <c r="J13" s="111"/>
     </row>
     <row r="14" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A14" s="113" t="s">
+      <c r="A14" s="112" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="114"/>
-      <c r="C14" s="114"/>
-      <c r="D14" s="114"/>
-      <c r="E14" s="114"/>
-      <c r="F14" s="114"/>
-      <c r="G14" s="114"/>
-      <c r="H14" s="114"/>
-      <c r="I14" s="114"/>
-      <c r="J14" s="115"/>
+      <c r="B14" s="113"/>
+      <c r="C14" s="113"/>
+      <c r="D14" s="113"/>
+      <c r="E14" s="113"/>
+      <c r="F14" s="113"/>
+      <c r="G14" s="113"/>
+      <c r="H14" s="113"/>
+      <c r="I14" s="113"/>
+      <c r="J14" s="114"/>
     </row>
     <row r="15" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A15" s="95" t="s">
+      <c r="A15" s="94" t="s">
         <v>26</v>
       </c>
       <c r="B15" s="42"/>
       <c r="C15" s="43"/>
-      <c r="D15" s="55" t="s">
-        <v>82</v>
+      <c r="D15" s="82" t="s">
+        <v>90</v>
       </c>
       <c r="E15" s="42"/>
       <c r="F15" s="42"/>
@@ -7647,11 +7647,11 @@
         <v>27</v>
       </c>
       <c r="J15" s="38" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A16" s="95" t="s">
+      <c r="A16" s="94" t="s">
         <v>28</v>
       </c>
       <c r="B16" s="42"/>
@@ -7668,14 +7668,14 @@
       <c r="G16" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H16" s="96" t="s">
+      <c r="H16" s="115" t="s">
         <v>19</v>
       </c>
       <c r="I16" s="42"/>
-      <c r="J16" s="56"/>
+      <c r="J16" s="63"/>
     </row>
     <row r="17" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A17" s="92" t="s">
+      <c r="A17" s="102" t="s">
         <v>71</v>
       </c>
       <c r="B17" s="42"/>
@@ -7690,14 +7690,14 @@
       <c r="G17" s="17" t="s">
         <v>75</v>
       </c>
-      <c r="H17" s="55" t="s">
+      <c r="H17" s="82" t="s">
         <v>78</v>
       </c>
       <c r="I17" s="42"/>
-      <c r="J17" s="56"/>
+      <c r="J17" s="63"/>
     </row>
     <row r="18" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A18" s="95" t="s">
+      <c r="A18" s="94" t="s">
         <v>25</v>
       </c>
       <c r="B18" s="42"/>
@@ -7708,16 +7708,16 @@
       <c r="G18" s="42"/>
       <c r="H18" s="42"/>
       <c r="I18" s="42"/>
-      <c r="J18" s="56"/>
+      <c r="J18" s="63"/>
     </row>
     <row r="19" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A19" s="95" t="s">
+      <c r="A19" s="94" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="42"/>
       <c r="C19" s="43"/>
-      <c r="D19" s="55" t="s">
-        <v>89</v>
+      <c r="D19" s="82" t="s">
+        <v>87</v>
       </c>
       <c r="E19" s="42"/>
       <c r="F19" s="42"/>
@@ -7727,11 +7727,11 @@
         <v>27</v>
       </c>
       <c r="J19" s="38" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A20" s="95" t="s">
+      <c r="A20" s="94" t="s">
         <v>28</v>
       </c>
       <c r="B20" s="42"/>
@@ -7748,18 +7748,18 @@
       <c r="G20" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H20" s="96" t="s">
+      <c r="H20" s="115" t="s">
         <v>19</v>
       </c>
       <c r="I20" s="42"/>
-      <c r="J20" s="56"/>
+      <c r="J20" s="63"/>
     </row>
     <row r="21" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A21" s="92" t="s">
+      <c r="A21" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="B21" s="93"/>
-      <c r="C21" s="94"/>
+      <c r="B21" s="118"/>
+      <c r="C21" s="119"/>
       <c r="D21" s="16"/>
       <c r="E21" s="16" t="s">
         <v>74</v>
@@ -7770,14 +7770,14 @@
       <c r="G21" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="H21" s="55" t="s">
+      <c r="H21" s="82" t="s">
         <v>79</v>
       </c>
-      <c r="I21" s="58"/>
-      <c r="J21" s="59"/>
+      <c r="I21" s="83"/>
+      <c r="J21" s="84"/>
     </row>
     <row r="22" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A22" s="95" t="s">
+      <c r="A22" s="94" t="s">
         <v>25</v>
       </c>
       <c r="B22" s="42"/>
@@ -7788,16 +7788,16 @@
       <c r="G22" s="42"/>
       <c r="H22" s="42"/>
       <c r="I22" s="42"/>
-      <c r="J22" s="56"/>
+      <c r="J22" s="63"/>
     </row>
     <row r="23" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A23" s="95" t="s">
+      <c r="A23" s="94" t="s">
         <v>26</v>
       </c>
       <c r="B23" s="42"/>
       <c r="C23" s="43"/>
-      <c r="D23" s="55" t="s">
-        <v>84</v>
+      <c r="D23" s="82" t="s">
+        <v>89</v>
       </c>
       <c r="E23" s="42"/>
       <c r="F23" s="42"/>
@@ -7807,11 +7807,11 @@
         <v>27</v>
       </c>
       <c r="J23" s="38" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A24" s="95" t="s">
+      <c r="A24" s="94" t="s">
         <v>28</v>
       </c>
       <c r="B24" s="42"/>
@@ -7828,18 +7828,18 @@
       <c r="G24" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="H24" s="96" t="s">
+      <c r="H24" s="115" t="s">
         <v>19</v>
       </c>
       <c r="I24" s="42"/>
-      <c r="J24" s="56"/>
+      <c r="J24" s="63"/>
     </row>
     <row r="25" spans="1:10" ht="19.5" customHeight="1">
-      <c r="A25" s="92" t="s">
+      <c r="A25" s="102" t="s">
         <v>73</v>
       </c>
-      <c r="B25" s="93"/>
-      <c r="C25" s="94"/>
+      <c r="B25" s="118"/>
+      <c r="C25" s="119"/>
       <c r="D25" s="16"/>
       <c r="E25" s="16" t="s">
         <v>74</v>
@@ -7850,23 +7850,23 @@
       <c r="G25" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="H25" s="55" t="s">
+      <c r="H25" s="82" t="s">
         <v>80</v>
       </c>
-      <c r="I25" s="58"/>
-      <c r="J25" s="59"/>
+      <c r="I25" s="83"/>
+      <c r="J25" s="84"/>
     </row>
     <row r="26" spans="1:10" ht="19.5" customHeight="1" thickBot="1">
-      <c r="A26" s="99"/>
-      <c r="B26" s="100"/>
-      <c r="C26" s="101"/>
+      <c r="A26" s="120"/>
+      <c r="B26" s="121"/>
+      <c r="C26" s="122"/>
       <c r="D26" s="39"/>
       <c r="E26" s="39"/>
       <c r="F26" s="40"/>
       <c r="G26" s="40"/>
-      <c r="H26" s="49"/>
-      <c r="I26" s="97"/>
-      <c r="J26" s="98"/>
+      <c r="H26" s="78"/>
+      <c r="I26" s="116"/>
+      <c r="J26" s="117"/>
     </row>
     <row r="27" spans="1:10" ht="12.75" customHeight="1"/>
     <row r="28" spans="1:10" ht="12.75" customHeight="1"/>
@@ -8841,6 +8841,30 @@
     <row r="997" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="35">
+    <mergeCell ref="H21:J21"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A19:C19"/>
+    <mergeCell ref="A18:J18"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="H20:J20"/>
+    <mergeCell ref="H25:J25"/>
+    <mergeCell ref="H26:J26"/>
+    <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A22:J22"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="H24:J24"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="D5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J13"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="H16:J16"/>
+    <mergeCell ref="H17:J17"/>
     <mergeCell ref="J2:J4"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="D15:H15"/>
@@ -8852,30 +8876,6 @@
     <mergeCell ref="F2:G4"/>
     <mergeCell ref="H2:H4"/>
     <mergeCell ref="I2:I4"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="D5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J13"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="H16:J16"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="H26:J26"/>
-    <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A22:J22"/>
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="A24:C24"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="H24:J24"/>
-    <mergeCell ref="H21:J21"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A19:C19"/>
-    <mergeCell ref="A18:J18"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="H20:J20"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -8895,84 +8895,84 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="18" customHeight="1">
-      <c r="A1" s="62" t="s">
+      <c r="A1" s="67" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="D1" s="63"/>
-      <c r="E1" s="63"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="79" t="s">
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="69"/>
+      <c r="G1" s="49" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="80"/>
-      <c r="K1" s="79" t="s">
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
+      <c r="J1" s="50"/>
+      <c r="K1" s="49" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="103"/>
-      <c r="M1" s="103"/>
-      <c r="N1" s="80"/>
-      <c r="O1" s="79" t="s">
+      <c r="L1" s="100"/>
+      <c r="M1" s="100"/>
+      <c r="N1" s="50"/>
+      <c r="O1" s="49" t="s">
         <v>7</v>
       </c>
-      <c r="P1" s="80"/>
-      <c r="Q1" s="79" t="s">
+      <c r="P1" s="50"/>
+      <c r="Q1" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="R1" s="80"/>
-      <c r="S1" s="79" t="s">
+      <c r="R1" s="50"/>
+      <c r="S1" s="49" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="133"/>
+      <c r="T1" s="132"/>
     </row>
     <row r="2" spans="1:26" ht="18" customHeight="1">
-      <c r="A2" s="65"/>
+      <c r="A2" s="70"/>
       <c r="B2" s="45"/>
       <c r="C2" s="45"/>
       <c r="D2" s="45"/>
       <c r="E2" s="45"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="81" t="s">
+      <c r="F2" s="54"/>
+      <c r="G2" s="51" t="s">
         <v>67</v>
       </c>
       <c r="H2" s="106"/>
       <c r="I2" s="106"/>
-      <c r="J2" s="82"/>
-      <c r="K2" s="81"/>
+      <c r="J2" s="52"/>
+      <c r="K2" s="51"/>
       <c r="L2" s="106"/>
       <c r="M2" s="106"/>
-      <c r="N2" s="82"/>
-      <c r="O2" s="81"/>
-      <c r="P2" s="82"/>
-      <c r="Q2" s="81"/>
-      <c r="R2" s="82"/>
-      <c r="S2" s="81"/>
-      <c r="T2" s="138"/>
+      <c r="N2" s="52"/>
+      <c r="O2" s="51"/>
+      <c r="P2" s="52"/>
+      <c r="Q2" s="51"/>
+      <c r="R2" s="52"/>
+      <c r="S2" s="51"/>
+      <c r="T2" s="129"/>
     </row>
     <row r="3" spans="1:26" ht="18" customHeight="1">
-      <c r="A3" s="65"/>
+      <c r="A3" s="70"/>
       <c r="B3" s="45"/>
       <c r="C3" s="45"/>
       <c r="D3" s="45"/>
       <c r="E3" s="45"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="83"/>
+      <c r="F3" s="54"/>
+      <c r="G3" s="53"/>
       <c r="H3" s="45"/>
       <c r="I3" s="45"/>
-      <c r="J3" s="66"/>
-      <c r="K3" s="83"/>
+      <c r="J3" s="54"/>
+      <c r="K3" s="53"/>
       <c r="L3" s="45"/>
       <c r="M3" s="45"/>
-      <c r="N3" s="66"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="66"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="66"/>
-      <c r="S3" s="83"/>
-      <c r="T3" s="139"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="53"/>
+      <c r="P3" s="54"/>
+      <c r="Q3" s="53"/>
+      <c r="R3" s="54"/>
+      <c r="S3" s="53"/>
+      <c r="T3" s="130"/>
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1">
       <c r="A4" s="88"/>
@@ -8994,36 +8994,36 @@
       <c r="Q4" s="91"/>
       <c r="R4" s="90"/>
       <c r="S4" s="91"/>
-      <c r="T4" s="140"/>
+      <c r="T4" s="131"/>
     </row>
     <row r="5" spans="1:26" ht="18" customHeight="1">
-      <c r="A5" s="131" t="s">
+      <c r="A5" s="133" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="103"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="103"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="80"/>
-      <c r="G5" s="132" t="s">
+      <c r="B5" s="100"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="100"/>
+      <c r="E5" s="100"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="134" t="s">
         <v>35</v>
       </c>
-      <c r="H5" s="103"/>
-      <c r="I5" s="103"/>
-      <c r="J5" s="103"/>
-      <c r="K5" s="103"/>
-      <c r="L5" s="103"/>
-      <c r="M5" s="103"/>
-      <c r="N5" s="103"/>
-      <c r="O5" s="103"/>
-      <c r="P5" s="103"/>
-      <c r="Q5" s="103"/>
-      <c r="R5" s="103"/>
-      <c r="S5" s="103"/>
-      <c r="T5" s="133"/>
+      <c r="H5" s="100"/>
+      <c r="I5" s="100"/>
+      <c r="J5" s="100"/>
+      <c r="K5" s="100"/>
+      <c r="L5" s="100"/>
+      <c r="M5" s="100"/>
+      <c r="N5" s="100"/>
+      <c r="O5" s="100"/>
+      <c r="P5" s="100"/>
+      <c r="Q5" s="100"/>
+      <c r="R5" s="100"/>
+      <c r="S5" s="100"/>
+      <c r="T5" s="132"/>
     </row>
     <row r="6" spans="1:26" ht="18" customHeight="1">
-      <c r="A6" s="134" t="s">
+      <c r="A6" s="135" t="s">
         <v>36</v>
       </c>
       <c r="B6" s="42"/>
@@ -9031,7 +9031,7 @@
       <c r="D6" s="42"/>
       <c r="E6" s="42"/>
       <c r="F6" s="43"/>
-      <c r="G6" s="55" t="s">
+      <c r="G6" s="82" t="s">
         <v>20</v>
       </c>
       <c r="H6" s="42"/>
@@ -9046,10 +9046,10 @@
       <c r="Q6" s="42"/>
       <c r="R6" s="42"/>
       <c r="S6" s="42"/>
-      <c r="T6" s="135"/>
+      <c r="T6" s="136"/>
     </row>
     <row r="7" spans="1:26" ht="18" customHeight="1">
-      <c r="A7" s="134" t="s">
+      <c r="A7" s="135" t="s">
         <v>37</v>
       </c>
       <c r="B7" s="42"/>
@@ -9057,7 +9057,7 @@
       <c r="D7" s="42"/>
       <c r="E7" s="42"/>
       <c r="F7" s="43"/>
-      <c r="G7" s="55" t="s">
+      <c r="G7" s="82" t="s">
         <v>38</v>
       </c>
       <c r="H7" s="42"/>
@@ -9072,7 +9072,7 @@
       <c r="Q7" s="42"/>
       <c r="R7" s="42"/>
       <c r="S7" s="42"/>
-      <c r="T7" s="135"/>
+      <c r="T7" s="136"/>
     </row>
     <row r="8" spans="1:26" ht="7.5" customHeight="1">
       <c r="A8" s="8"/>
@@ -9271,33 +9271,33 @@
       <c r="T14" s="10"/>
     </row>
     <row r="15" spans="1:26" ht="18.75" customHeight="1">
-      <c r="A15" s="134" t="s">
+      <c r="A15" s="135" t="s">
         <v>45</v>
       </c>
       <c r="B15" s="43"/>
-      <c r="C15" s="137" t="s">
+      <c r="C15" s="139" t="s">
         <v>39</v>
       </c>
       <c r="D15" s="43"/>
-      <c r="E15" s="96" t="s">
+      <c r="E15" s="115" t="s">
         <v>46</v>
       </c>
       <c r="F15" s="43"/>
-      <c r="G15" s="96" t="s">
+      <c r="G15" s="115" t="s">
         <v>47</v>
       </c>
       <c r="H15" s="42"/>
       <c r="I15" s="43"/>
-      <c r="J15" s="96" t="s">
+      <c r="J15" s="115" t="s">
         <v>48</v>
       </c>
       <c r="K15" s="43"/>
-      <c r="L15" s="96" t="s">
+      <c r="L15" s="115" t="s">
         <v>49</v>
       </c>
       <c r="M15" s="42"/>
       <c r="N15" s="43"/>
-      <c r="O15" s="96" t="s">
+      <c r="O15" s="115" t="s">
         <v>50</v>
       </c>
       <c r="P15" s="42"/>
@@ -9313,33 +9313,33 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="48" customHeight="1">
-      <c r="A16" s="123">
+      <c r="A16" s="137">
         <v>1</v>
       </c>
       <c r="B16" s="43"/>
-      <c r="C16" s="124" t="s">
+      <c r="C16" s="138" t="s">
         <v>54</v>
       </c>
       <c r="D16" s="43"/>
-      <c r="E16" s="124" t="s">
+      <c r="E16" s="138" t="s">
         <v>55</v>
       </c>
       <c r="F16" s="43"/>
-      <c r="G16" s="136" t="s">
+      <c r="G16" s="123" t="s">
         <v>56</v>
       </c>
       <c r="H16" s="42"/>
       <c r="I16" s="43"/>
-      <c r="J16" s="136" t="s">
+      <c r="J16" s="123" t="s">
         <v>57</v>
       </c>
       <c r="K16" s="43"/>
-      <c r="L16" s="128" t="s">
+      <c r="L16" s="127" t="s">
         <v>58</v>
       </c>
       <c r="M16" s="42"/>
       <c r="N16" s="43"/>
-      <c r="O16" s="128" t="s">
+      <c r="O16" s="127" t="s">
         <v>59</v>
       </c>
       <c r="P16" s="42"/>
@@ -9355,33 +9355,33 @@
       <c r="Z16" s="32"/>
     </row>
     <row r="17" spans="1:26" ht="41.25" customHeight="1">
-      <c r="A17" s="123">
+      <c r="A17" s="137">
         <v>2</v>
       </c>
       <c r="B17" s="43"/>
-      <c r="C17" s="124" t="s">
+      <c r="C17" s="138" t="s">
         <v>60</v>
       </c>
       <c r="D17" s="43"/>
-      <c r="E17" s="124" t="s">
+      <c r="E17" s="138" t="s">
         <v>61</v>
       </c>
       <c r="F17" s="43"/>
-      <c r="G17" s="136" t="s">
+      <c r="G17" s="123" t="s">
         <v>62</v>
       </c>
       <c r="H17" s="42"/>
       <c r="I17" s="43"/>
-      <c r="J17" s="136" t="s">
+      <c r="J17" s="123" t="s">
         <v>63</v>
       </c>
       <c r="K17" s="43"/>
-      <c r="L17" s="128" t="s">
+      <c r="L17" s="127" t="s">
         <v>64</v>
       </c>
       <c r="M17" s="42"/>
       <c r="N17" s="43"/>
-      <c r="O17" s="128" t="s">
+      <c r="O17" s="127" t="s">
         <v>65</v>
       </c>
       <c r="P17" s="42"/>
@@ -9397,23 +9397,23 @@
       <c r="Z17" s="32"/>
     </row>
     <row r="18" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A18" s="123"/>
+      <c r="A18" s="137"/>
       <c r="B18" s="43"/>
-      <c r="C18" s="124"/>
+      <c r="C18" s="138"/>
       <c r="D18" s="43"/>
-      <c r="E18" s="124"/>
+      <c r="E18" s="138"/>
       <c r="F18" s="43"/>
-      <c r="G18" s="136" t="s">
+      <c r="G18" s="123" t="s">
         <v>69</v>
       </c>
       <c r="H18" s="42"/>
       <c r="I18" s="43"/>
-      <c r="J18" s="136"/>
+      <c r="J18" s="123"/>
       <c r="K18" s="43"/>
-      <c r="L18" s="128"/>
+      <c r="L18" s="127"/>
       <c r="M18" s="42"/>
       <c r="N18" s="43"/>
-      <c r="O18" s="128"/>
+      <c r="O18" s="127"/>
       <c r="P18" s="42"/>
       <c r="Q18" s="43"/>
       <c r="R18" s="30"/>
@@ -9427,23 +9427,23 @@
       <c r="Z18" s="32"/>
     </row>
     <row r="19" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A19" s="123"/>
+      <c r="A19" s="137"/>
       <c r="B19" s="43"/>
-      <c r="C19" s="124"/>
+      <c r="C19" s="138"/>
       <c r="D19" s="43"/>
-      <c r="E19" s="124"/>
+      <c r="E19" s="138"/>
       <c r="F19" s="43"/>
-      <c r="G19" s="136" t="s">
+      <c r="G19" s="123" t="s">
         <v>70</v>
       </c>
       <c r="H19" s="42"/>
       <c r="I19" s="43"/>
-      <c r="J19" s="136"/>
+      <c r="J19" s="123"/>
       <c r="K19" s="43"/>
-      <c r="L19" s="128"/>
+      <c r="L19" s="127"/>
       <c r="M19" s="42"/>
       <c r="N19" s="43"/>
-      <c r="O19" s="128"/>
+      <c r="O19" s="127"/>
       <c r="P19" s="42"/>
       <c r="Q19" s="43"/>
       <c r="R19" s="30"/>
@@ -9457,21 +9457,21 @@
       <c r="Z19" s="32"/>
     </row>
     <row r="20" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A20" s="123"/>
+      <c r="A20" s="137"/>
       <c r="B20" s="43"/>
-      <c r="C20" s="124"/>
+      <c r="C20" s="138"/>
       <c r="D20" s="43"/>
-      <c r="E20" s="124"/>
+      <c r="E20" s="138"/>
       <c r="F20" s="43"/>
-      <c r="G20" s="136"/>
+      <c r="G20" s="123"/>
       <c r="H20" s="42"/>
       <c r="I20" s="43"/>
-      <c r="J20" s="136"/>
+      <c r="J20" s="123"/>
       <c r="K20" s="43"/>
-      <c r="L20" s="128"/>
+      <c r="L20" s="127"/>
       <c r="M20" s="42"/>
       <c r="N20" s="43"/>
-      <c r="O20" s="128"/>
+      <c r="O20" s="127"/>
       <c r="P20" s="42"/>
       <c r="Q20" s="43"/>
       <c r="R20" s="30"/>
@@ -9485,21 +9485,21 @@
       <c r="Z20" s="32"/>
     </row>
     <row r="21" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A21" s="123"/>
+      <c r="A21" s="137"/>
       <c r="B21" s="43"/>
-      <c r="C21" s="124"/>
+      <c r="C21" s="138"/>
       <c r="D21" s="43"/>
-      <c r="E21" s="124"/>
+      <c r="E21" s="138"/>
       <c r="F21" s="43"/>
-      <c r="G21" s="136"/>
+      <c r="G21" s="123"/>
       <c r="H21" s="42"/>
       <c r="I21" s="43"/>
-      <c r="J21" s="136"/>
+      <c r="J21" s="123"/>
       <c r="K21" s="43"/>
-      <c r="L21" s="128"/>
+      <c r="L21" s="127"/>
       <c r="M21" s="42"/>
       <c r="N21" s="43"/>
-      <c r="O21" s="128"/>
+      <c r="O21" s="127"/>
       <c r="P21" s="42"/>
       <c r="Q21" s="43"/>
       <c r="R21" s="30"/>
@@ -9513,21 +9513,21 @@
       <c r="Z21" s="32"/>
     </row>
     <row r="22" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A22" s="123"/>
+      <c r="A22" s="137"/>
       <c r="B22" s="43"/>
-      <c r="C22" s="124"/>
+      <c r="C22" s="138"/>
       <c r="D22" s="43"/>
-      <c r="E22" s="124"/>
+      <c r="E22" s="138"/>
       <c r="F22" s="43"/>
-      <c r="G22" s="136"/>
+      <c r="G22" s="123"/>
       <c r="H22" s="42"/>
       <c r="I22" s="43"/>
-      <c r="J22" s="136"/>
+      <c r="J22" s="123"/>
       <c r="K22" s="43"/>
-      <c r="L22" s="128"/>
+      <c r="L22" s="127"/>
       <c r="M22" s="42"/>
       <c r="N22" s="43"/>
-      <c r="O22" s="128"/>
+      <c r="O22" s="127"/>
       <c r="P22" s="42"/>
       <c r="Q22" s="43"/>
       <c r="R22" s="30"/>
@@ -9541,21 +9541,21 @@
       <c r="Z22" s="32"/>
     </row>
     <row r="23" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A23" s="123"/>
+      <c r="A23" s="137"/>
       <c r="B23" s="43"/>
-      <c r="C23" s="124"/>
+      <c r="C23" s="138"/>
       <c r="D23" s="43"/>
-      <c r="E23" s="124"/>
+      <c r="E23" s="138"/>
       <c r="F23" s="43"/>
-      <c r="G23" s="136"/>
+      <c r="G23" s="123"/>
       <c r="H23" s="42"/>
       <c r="I23" s="43"/>
-      <c r="J23" s="136"/>
+      <c r="J23" s="123"/>
       <c r="K23" s="43"/>
-      <c r="L23" s="128"/>
+      <c r="L23" s="127"/>
       <c r="M23" s="42"/>
       <c r="N23" s="43"/>
-      <c r="O23" s="128"/>
+      <c r="O23" s="127"/>
       <c r="P23" s="42"/>
       <c r="Q23" s="43"/>
       <c r="R23" s="30"/>
@@ -9569,21 +9569,21 @@
       <c r="Z23" s="32"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A24" s="123"/>
+      <c r="A24" s="137"/>
       <c r="B24" s="43"/>
-      <c r="C24" s="124"/>
+      <c r="C24" s="138"/>
       <c r="D24" s="43"/>
-      <c r="E24" s="124"/>
+      <c r="E24" s="138"/>
       <c r="F24" s="43"/>
-      <c r="G24" s="136"/>
+      <c r="G24" s="123"/>
       <c r="H24" s="42"/>
       <c r="I24" s="43"/>
-      <c r="J24" s="136"/>
+      <c r="J24" s="123"/>
       <c r="K24" s="43"/>
-      <c r="L24" s="128"/>
+      <c r="L24" s="127"/>
       <c r="M24" s="42"/>
       <c r="N24" s="43"/>
-      <c r="O24" s="128"/>
+      <c r="O24" s="127"/>
       <c r="P24" s="42"/>
       <c r="Q24" s="43"/>
       <c r="R24" s="30"/>
@@ -9597,21 +9597,21 @@
       <c r="Z24" s="32"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A25" s="123"/>
+      <c r="A25" s="137"/>
       <c r="B25" s="43"/>
-      <c r="C25" s="124"/>
+      <c r="C25" s="138"/>
       <c r="D25" s="43"/>
-      <c r="E25" s="124"/>
+      <c r="E25" s="138"/>
       <c r="F25" s="43"/>
-      <c r="G25" s="136"/>
+      <c r="G25" s="123"/>
       <c r="H25" s="42"/>
       <c r="I25" s="43"/>
-      <c r="J25" s="136"/>
+      <c r="J25" s="123"/>
       <c r="K25" s="43"/>
-      <c r="L25" s="128"/>
+      <c r="L25" s="127"/>
       <c r="M25" s="42"/>
       <c r="N25" s="43"/>
-      <c r="O25" s="128"/>
+      <c r="O25" s="127"/>
       <c r="P25" s="42"/>
       <c r="Q25" s="43"/>
       <c r="R25" s="30"/>
@@ -9625,21 +9625,21 @@
       <c r="Z25" s="32"/>
     </row>
     <row r="26" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A26" s="123"/>
+      <c r="A26" s="137"/>
       <c r="B26" s="43"/>
-      <c r="C26" s="124"/>
+      <c r="C26" s="138"/>
       <c r="D26" s="43"/>
-      <c r="E26" s="124"/>
+      <c r="E26" s="138"/>
       <c r="F26" s="43"/>
-      <c r="G26" s="136"/>
+      <c r="G26" s="123"/>
       <c r="H26" s="42"/>
       <c r="I26" s="43"/>
-      <c r="J26" s="136"/>
+      <c r="J26" s="123"/>
       <c r="K26" s="43"/>
-      <c r="L26" s="128"/>
+      <c r="L26" s="127"/>
       <c r="M26" s="42"/>
       <c r="N26" s="43"/>
-      <c r="O26" s="128"/>
+      <c r="O26" s="127"/>
       <c r="P26" s="42"/>
       <c r="Q26" s="43"/>
       <c r="R26" s="30"/>
@@ -9653,21 +9653,21 @@
       <c r="Z26" s="32"/>
     </row>
     <row r="27" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A27" s="123"/>
+      <c r="A27" s="137"/>
       <c r="B27" s="43"/>
-      <c r="C27" s="124"/>
+      <c r="C27" s="138"/>
       <c r="D27" s="43"/>
-      <c r="E27" s="124"/>
+      <c r="E27" s="138"/>
       <c r="F27" s="43"/>
-      <c r="G27" s="136"/>
+      <c r="G27" s="123"/>
       <c r="H27" s="42"/>
       <c r="I27" s="43"/>
-      <c r="J27" s="136"/>
+      <c r="J27" s="123"/>
       <c r="K27" s="43"/>
-      <c r="L27" s="128"/>
+      <c r="L27" s="127"/>
       <c r="M27" s="42"/>
       <c r="N27" s="43"/>
-      <c r="O27" s="128"/>
+      <c r="O27" s="127"/>
       <c r="P27" s="42"/>
       <c r="Q27" s="43"/>
       <c r="R27" s="30"/>
@@ -9681,21 +9681,21 @@
       <c r="Z27" s="32"/>
     </row>
     <row r="28" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A28" s="123"/>
+      <c r="A28" s="137"/>
       <c r="B28" s="43"/>
-      <c r="C28" s="124"/>
+      <c r="C28" s="138"/>
       <c r="D28" s="43"/>
-      <c r="E28" s="124"/>
+      <c r="E28" s="138"/>
       <c r="F28" s="43"/>
-      <c r="G28" s="136"/>
+      <c r="G28" s="123"/>
       <c r="H28" s="42"/>
       <c r="I28" s="43"/>
-      <c r="J28" s="136"/>
+      <c r="J28" s="123"/>
       <c r="K28" s="43"/>
-      <c r="L28" s="128"/>
+      <c r="L28" s="127"/>
       <c r="M28" s="42"/>
       <c r="N28" s="43"/>
-      <c r="O28" s="128"/>
+      <c r="O28" s="127"/>
       <c r="P28" s="42"/>
       <c r="Q28" s="43"/>
       <c r="R28" s="30"/>
@@ -9709,21 +9709,21 @@
       <c r="Z28" s="32"/>
     </row>
     <row r="29" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A29" s="123"/>
+      <c r="A29" s="137"/>
       <c r="B29" s="43"/>
-      <c r="C29" s="124"/>
+      <c r="C29" s="138"/>
       <c r="D29" s="43"/>
-      <c r="E29" s="124"/>
+      <c r="E29" s="138"/>
       <c r="F29" s="43"/>
-      <c r="G29" s="136"/>
+      <c r="G29" s="123"/>
       <c r="H29" s="42"/>
       <c r="I29" s="43"/>
-      <c r="J29" s="136"/>
+      <c r="J29" s="123"/>
       <c r="K29" s="43"/>
-      <c r="L29" s="128"/>
+      <c r="L29" s="127"/>
       <c r="M29" s="42"/>
       <c r="N29" s="43"/>
-      <c r="O29" s="128"/>
+      <c r="O29" s="127"/>
       <c r="P29" s="42"/>
       <c r="Q29" s="43"/>
       <c r="R29" s="30"/>
@@ -9737,21 +9737,21 @@
       <c r="Z29" s="32"/>
     </row>
     <row r="30" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A30" s="123"/>
+      <c r="A30" s="137"/>
       <c r="B30" s="43"/>
-      <c r="C30" s="124"/>
+      <c r="C30" s="138"/>
       <c r="D30" s="43"/>
-      <c r="E30" s="124"/>
+      <c r="E30" s="138"/>
       <c r="F30" s="43"/>
-      <c r="G30" s="136"/>
+      <c r="G30" s="123"/>
       <c r="H30" s="42"/>
       <c r="I30" s="43"/>
-      <c r="J30" s="136"/>
+      <c r="J30" s="123"/>
       <c r="K30" s="43"/>
-      <c r="L30" s="128"/>
+      <c r="L30" s="127"/>
       <c r="M30" s="42"/>
       <c r="N30" s="43"/>
-      <c r="O30" s="128"/>
+      <c r="O30" s="127"/>
       <c r="P30" s="42"/>
       <c r="Q30" s="43"/>
       <c r="R30" s="30"/>
@@ -9765,22 +9765,22 @@
       <c r="Z30" s="32"/>
     </row>
     <row r="31" spans="1:26" ht="12.75" customHeight="1">
-      <c r="A31" s="125"/>
+      <c r="A31" s="140"/>
       <c r="B31" s="126"/>
-      <c r="C31" s="127"/>
+      <c r="C31" s="141"/>
       <c r="D31" s="126"/>
-      <c r="E31" s="127"/>
+      <c r="E31" s="141"/>
       <c r="F31" s="126"/>
-      <c r="G31" s="141"/>
-      <c r="H31" s="130"/>
+      <c r="G31" s="124"/>
+      <c r="H31" s="125"/>
       <c r="I31" s="126"/>
-      <c r="J31" s="141"/>
+      <c r="J31" s="124"/>
       <c r="K31" s="126"/>
-      <c r="L31" s="129"/>
-      <c r="M31" s="130"/>
+      <c r="L31" s="128"/>
+      <c r="M31" s="125"/>
       <c r="N31" s="126"/>
-      <c r="O31" s="129"/>
-      <c r="P31" s="130"/>
+      <c r="O31" s="128"/>
+      <c r="P31" s="125"/>
       <c r="Q31" s="126"/>
       <c r="R31" s="33"/>
       <c r="S31" s="33"/>
@@ -10779,62 +10779,62 @@
     <row r="1000" ht="12.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="136">
-    <mergeCell ref="G15:I15"/>
-    <mergeCell ref="J15:K15"/>
-    <mergeCell ref="G16:I16"/>
-    <mergeCell ref="J16:K16"/>
-    <mergeCell ref="G17:I17"/>
-    <mergeCell ref="J17:K17"/>
-    <mergeCell ref="J18:K18"/>
-    <mergeCell ref="G18:I18"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="G21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="G22:I22"/>
-    <mergeCell ref="J22:K22"/>
-    <mergeCell ref="G23:I23"/>
-    <mergeCell ref="J23:K23"/>
-    <mergeCell ref="G24:I24"/>
-    <mergeCell ref="J24:K24"/>
-    <mergeCell ref="G25:I25"/>
-    <mergeCell ref="J25:K25"/>
-    <mergeCell ref="J26:K26"/>
-    <mergeCell ref="G30:I30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="G31:I31"/>
-    <mergeCell ref="J31:K31"/>
-    <mergeCell ref="G26:I26"/>
-    <mergeCell ref="G27:I27"/>
-    <mergeCell ref="J27:K27"/>
-    <mergeCell ref="G28:I28"/>
-    <mergeCell ref="J28:K28"/>
-    <mergeCell ref="G29:I29"/>
-    <mergeCell ref="J29:K29"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
-    <mergeCell ref="L28:N28"/>
-    <mergeCell ref="L29:N29"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="L31:N31"/>
-    <mergeCell ref="L18:N18"/>
-    <mergeCell ref="L19:N19"/>
-    <mergeCell ref="L21:N21"/>
-    <mergeCell ref="L22:N22"/>
-    <mergeCell ref="L23:N23"/>
-    <mergeCell ref="L24:N24"/>
-    <mergeCell ref="L25:N25"/>
-    <mergeCell ref="K2:N4"/>
-    <mergeCell ref="O2:P4"/>
-    <mergeCell ref="Q2:R4"/>
-    <mergeCell ref="S2:T4"/>
-    <mergeCell ref="A1:F4"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="K1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="A30:B30"/>
+    <mergeCell ref="C30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:D31"/>
+    <mergeCell ref="E31:F31"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="C23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="C22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="E19:F19"/>
+    <mergeCell ref="O27:Q27"/>
+    <mergeCell ref="O28:Q28"/>
+    <mergeCell ref="O29:Q29"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="O31:Q31"/>
+    <mergeCell ref="O19:Q19"/>
+    <mergeCell ref="O21:Q21"/>
+    <mergeCell ref="O22:Q22"/>
+    <mergeCell ref="O23:Q23"/>
+    <mergeCell ref="O24:Q24"/>
+    <mergeCell ref="O25:Q25"/>
+    <mergeCell ref="O26:Q26"/>
     <mergeCell ref="A5:F5"/>
     <mergeCell ref="G5:T5"/>
     <mergeCell ref="A6:F6"/>
@@ -10859,62 +10859,62 @@
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="E15:F15"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="O27:Q27"/>
-    <mergeCell ref="O28:Q28"/>
-    <mergeCell ref="O29:Q29"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="O31:Q31"/>
-    <mergeCell ref="O19:Q19"/>
-    <mergeCell ref="O21:Q21"/>
-    <mergeCell ref="O22:Q22"/>
-    <mergeCell ref="O23:Q23"/>
-    <mergeCell ref="O24:Q24"/>
-    <mergeCell ref="O25:Q25"/>
-    <mergeCell ref="O26:Q26"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
-    <mergeCell ref="E19:F19"/>
-    <mergeCell ref="C23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:D31"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="C29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="K2:N4"/>
+    <mergeCell ref="O2:P4"/>
+    <mergeCell ref="Q2:R4"/>
+    <mergeCell ref="S2:T4"/>
+    <mergeCell ref="A1:F4"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="G2:J4"/>
+    <mergeCell ref="L26:N26"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="L28:N28"/>
+    <mergeCell ref="L29:N29"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="L31:N31"/>
+    <mergeCell ref="L18:N18"/>
+    <mergeCell ref="L19:N19"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="L23:N23"/>
+    <mergeCell ref="L24:N24"/>
+    <mergeCell ref="L25:N25"/>
+    <mergeCell ref="J26:K26"/>
+    <mergeCell ref="G30:I30"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="G31:I31"/>
+    <mergeCell ref="J31:K31"/>
+    <mergeCell ref="G26:I26"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="J27:K27"/>
+    <mergeCell ref="G28:I28"/>
+    <mergeCell ref="J28:K28"/>
+    <mergeCell ref="G29:I29"/>
+    <mergeCell ref="J29:K29"/>
+    <mergeCell ref="G21:I21"/>
+    <mergeCell ref="J21:K21"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="G23:I23"/>
+    <mergeCell ref="J23:K23"/>
+    <mergeCell ref="G24:I24"/>
+    <mergeCell ref="J24:K24"/>
+    <mergeCell ref="G25:I25"/>
+    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="G15:I15"/>
+    <mergeCell ref="J15:K15"/>
+    <mergeCell ref="G16:I16"/>
+    <mergeCell ref="J16:K16"/>
+    <mergeCell ref="G17:I17"/>
+    <mergeCell ref="J17:K17"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="G18:I18"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="J19:K19"/>
   </mergeCells>
   <phoneticPr fontId="8"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
